--- a/byteCodeDemo.xlsx
+++ b/byteCodeDemo.xlsx
@@ -1,33 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="byteCodeDemo" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="45">
   <si>
     <t>CA</t>
   </si>
@@ -102,6 +89,9 @@
   </si>
   <si>
     <t>6C</t>
+  </si>
+  <si>
+    <t>常量池计数器</t>
   </si>
   <si>
     <t>2F</t>
@@ -164,7 +154,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -177,6 +167,34 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -193,6 +211,14 @@
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -232,21 +258,6 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -297,34 +308,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -351,13 +341,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -375,24 +413,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -411,18 +461,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -435,36 +473,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -483,24 +497,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -514,12 +516,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,6 +538,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -574,21 +585,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -647,152 +643,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -808,6 +804,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -815,12 +814,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
@@ -829,52 +834,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1071,7 +1076,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1080,7 +1085,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1366,7 +1371,7 @@
     <col min="20" max="20" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1379,81 +1384,81 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="E1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="11" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="3">
         <v>34</v>
       </c>
-      <c r="I1" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="4">
+      <c r="I1" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="5">
         <v>16</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="10" t="s">
+      <c r="L1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="13" t="s">
         <v>4</v>
       </c>
       <c r="O1" s="4">
         <v>12</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
-      <c r="A2" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="10" t="s">
+    <row r="2" spans="1:19">
+      <c r="A2" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="13" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="4">
         <v>13</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="13" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="4">
         <v>14</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="13" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="4">
         <v>15</v>
       </c>
-      <c r="K2" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="M2" s="10" t="s">
+      <c r="K2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="13" t="s">
         <v>8</v>
       </c>
       <c r="N2" s="4" t="s">
@@ -1465,30 +1470,30 @@
       <c r="P2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="S2" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="10" t="s">
+      <c r="A3" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="4">
         <v>49</v>
       </c>
-      <c r="E3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="10" t="s">
+      <c r="E3" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H3" s="4" t="s">
@@ -1509,23 +1514,23 @@
       <c r="M3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="O3" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="P3" s="10" t="s">
+      <c r="N3" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="7" t="s">
         <v>17</v>
       </c>
       <c r="T3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:19">
       <c r="A4" s="4">
         <v>28</v>
       </c>
@@ -1535,13 +1540,13 @@
       <c r="C4" s="4">
         <v>56</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="10" t="s">
+      <c r="D4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="4">
@@ -1556,10 +1561,10 @@
       <c r="J4" s="4">
         <v>65</v>
       </c>
-      <c r="K4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="L4" s="10" t="s">
+      <c r="K4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" s="13" t="s">
         <v>4</v>
       </c>
       <c r="M4" s="4" t="s">
@@ -1574,11 +1579,11 @@
       <c r="P4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="S4" s="7" t="s">
+      <c r="S4" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:19">
       <c r="A5" s="4">
         <v>65</v>
       </c>
@@ -1615,10 +1620,10 @@
       <c r="L5" s="4">
         <v>65</v>
       </c>
-      <c r="M5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="N5" s="10" t="s">
+      <c r="M5" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="N5" s="13" t="s">
         <v>4</v>
       </c>
       <c r="O5" s="4">
@@ -1627,8 +1632,11 @@
       <c r="P5" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="S5" s="9" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:16">
       <c r="A6" s="4" t="s">
         <v>19</v>
       </c>
@@ -1678,17 +1686,17 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:16">
       <c r="A7" s="4">
         <v>65</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="10" t="s">
+      <c r="B7" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="4">
@@ -1703,10 +1711,10 @@
       <c r="H7" s="4">
         <v>73</v>
       </c>
-      <c r="I7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="10" t="s">
+      <c r="I7" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="13" t="s">
         <v>4</v>
       </c>
       <c r="K7" s="4">
@@ -1728,7 +1736,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:16">
       <c r="A8" s="4">
         <v>30</v>
       </c>
@@ -1736,7 +1744,7 @@
         <v>32</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" s="4">
         <v>63</v>
@@ -1766,7 +1774,7 @@
         <v>31</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N8" s="4">
         <v>44</v>
@@ -1778,20 +1786,20 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:16">
       <c r="A9" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="4">
@@ -1803,13 +1811,13 @@
       <c r="H9" s="4">
         <v>64</v>
       </c>
-      <c r="I9" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="10" t="s">
+      <c r="I9" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="13" t="s">
         <v>8</v>
       </c>
       <c r="L9" s="4">
@@ -1821,14 +1829,14 @@
       <c r="N9" s="4">
         <v>49</v>
       </c>
-      <c r="O9" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="P9" s="10" t="s">
+      <c r="O9" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="P9" s="13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:16">
       <c r="A10" s="4" t="s">
         <v>5</v>
       </c>
@@ -1862,13 +1870,13 @@
       <c r="K10" s="4">
         <v>65</v>
       </c>
-      <c r="L10" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N10" s="10" t="s">
+      <c r="L10" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="M10" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="13" t="s">
         <v>7</v>
       </c>
       <c r="O10" s="4">
@@ -1878,7 +1886,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:16">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
@@ -1886,10 +1894,10 @@
         <v>19</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E11" s="4">
         <v>61</v>
@@ -1901,41 +1909,41 @@
         <v>61</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="J11" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="10" t="s">
+      <c r="K11" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="M11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="M11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N11" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="O11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="P11" s="10" t="s">
+      <c r="N11" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="O11" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="P11" s="13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
-      <c r="A12" s="10" t="s">
+    <row r="12" spans="1:16">
+      <c r="A12" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="10" t="s">
+      <c r="B12" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="4">
@@ -1960,7 +1968,7 @@
         <v>32</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L12" s="4">
         <v>63</v>
@@ -1978,7 +1986,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:16">
       <c r="A13" s="4">
         <v>65</v>
       </c>
@@ -1992,7 +2000,7 @@
         <v>31</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13" s="4">
         <v>44</v>
@@ -2006,17 +2014,17 @@
       <c r="I13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="K13" s="10" t="s">
+      <c r="J13" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="13" t="s">
         <v>4</v>
       </c>
       <c r="L13" s="4">
         <v>10</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N13" s="4">
         <v>61</v>
@@ -2028,9 +2036,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:16">
       <c r="A14" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>24</v>
@@ -2045,16 +2053,16 @@
         <v>67</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H14" s="4">
         <v>62</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J14" s="4">
         <v>65</v>
@@ -2065,263 +2073,263 @@
       <c r="L14" s="4">
         <v>74</v>
       </c>
-      <c r="M14" s="10" t="s">
+      <c r="M14" s="13" t="s">
         <v>4</v>
       </c>
       <c r="N14" s="4">
         <v>21</v>
       </c>
-      <c r="O14" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" s="10" t="s">
+      <c r="O14" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
-      <c r="A15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="10" t="s">
+    <row r="15" spans="1:16">
+      <c r="A15" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="10" t="s">
+      <c r="C15" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M15" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="K15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20">
-      <c r="A16" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="J16" s="10" t="s">
+      <c r="G16" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="J16" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="K16" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="L16" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="M16" s="10" t="s">
+      <c r="K16" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="M16" s="13" t="s">
         <v>4</v>
       </c>
       <c r="N16" s="4">
         <v>38</v>
       </c>
-      <c r="O16" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="P16" s="10" t="s">
-        <v>33</v>
+      <c r="O16" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="P16" s="13" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="10" t="s">
+      <c r="A17" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>4</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L17" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="N17" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="O17" s="10" t="s">
-        <v>33</v>
-      </c>
       <c r="P17" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="10" t="s">
+      <c r="A18" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="13" t="s">
         <v>4</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="10" t="s">
+      <c r="G18" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="13" t="s">
         <v>4</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K18" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="M18" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="10" t="s">
+      <c r="K18" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="M18" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="13" t="s">
         <v>4</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="10" t="s">
+      <c r="A19" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="13" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="4">
         <v>10</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="13" t="s">
         <v>4</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="I19" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="13" t="s">
         <v>4</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="M19" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N19" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="O19" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="L19" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="M19" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="O19" s="13" t="s">
         <v>4</v>
       </c>
       <c r="P19" s="4" t="s">
@@ -2329,152 +2337,152 @@
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="13" t="s">
         <v>4</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>4</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I20" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" s="13" t="s">
         <v>4</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K20" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K20" s="13" t="s">
         <v>4</v>
       </c>
       <c r="L20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="M20" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="O20" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="10" t="s">
+      <c r="M20" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="O20" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="13" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="10" t="s">
+      <c r="A21" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>4</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G21" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="10" t="s">
+      <c r="G21" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="13" t="s">
         <v>4</v>
       </c>
       <c r="L21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="P21" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="P21" s="13" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>31</v>
+      <c r="A22" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>32</v>
       </c>
       <c r="C22" s="4">
         <v>60</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>33</v>
+        <v>37</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="G22" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H22" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>33</v>
-      </c>
       <c r="K22" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="L22" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="O22" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="P22" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P22" s="13" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2482,131 +2490,131 @@
       <c r="A23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="10" t="s">
+      <c r="B23" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>4</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="J23" s="10" t="s">
+      <c r="F23" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="13" t="s">
         <v>4</v>
       </c>
       <c r="K23" s="4">
         <v>13</v>
       </c>
-      <c r="L23" s="10" t="s">
+      <c r="L23" s="13" t="s">
         <v>4</v>
       </c>
       <c r="M23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="N23" s="10" t="s">
+      <c r="N23" s="13" t="s">
         <v>4</v>
       </c>
       <c r="O23" s="4">
         <v>14</v>
       </c>
-      <c r="P23" s="10" t="s">
+      <c r="P23" s="13" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:16">
       <c r="A24" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="13" t="s">
         <v>4</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="H24" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="13" t="s">
         <v>4</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="L24" s="10" t="s">
+      <c r="L24" s="13" t="s">
         <v>4</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N24" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N24" s="13" t="s">
         <v>4</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="P24" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="P24" s="13" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="10" t="s">
+      <c r="A25" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="13" t="s">
         <v>4</v>
       </c>
       <c r="E25" s="4">
         <v>10</v>
       </c>
-      <c r="F25" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="J25" s="10" t="s">
+      <c r="F25" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J25" s="13" t="s">
         <v>4</v>
       </c>
       <c r="K25" s="4">

--- a/byteCodeDemo.xlsx
+++ b/byteCodeDemo.xlsx
@@ -13,8 +13,502 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>johnny.fei</author>
+  </authors>
+  <commentList>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+3</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+4</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+5</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+6</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+7</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+8</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+9</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+10</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+11</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+12</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+13</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+14</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+15</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+16</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+17</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+18</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+19</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+20</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+21</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>johnny.fei:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="46">
   <si>
     <t>CA</t>
   </si>
@@ -92,6 +586,9 @@
   </si>
   <si>
     <t>常量池计数器</t>
+  </si>
+  <si>
+    <t>这两个颜色交替表示常量池表中内容</t>
   </si>
   <si>
     <t>2F</t>
@@ -161,10 +658,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -313,8 +817,19 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -336,6 +851,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -646,10 +1173,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -658,36 +1185,33 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -697,98 +1221,101 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -801,12 +1328,21 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -816,13 +1352,25 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
@@ -1364,11 +1912,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T25"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="19" max="19" width="24.125" customWidth="1"/>
-    <col min="20" max="20" width="11.5" customWidth="1"/>
+    <col min="20" max="20" width="14.5" customWidth="1"/>
+    <col min="21" max="21" width="31.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1384,146 +1933,146 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="11" t="s">
+      <c r="E1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="16" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="3">
         <v>34</v>
       </c>
-      <c r="I1" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="5">
+      <c r="I1" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="7">
         <v>16</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="13" t="s">
+      <c r="L1" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="O1" s="4">
+      <c r="N1" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="O1" s="5">
         <v>12</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="19" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="19" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="4">
         <v>13</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="4">
+      <c r="F2" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="5">
         <v>14</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="19" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="4">
         <v>15</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="M2" s="13" t="s">
+      <c r="L2" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="5">
         <v>75</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="S2" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="B3" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="4">
         <v>49</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="13" t="s">
+      <c r="F3" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="5">
         <v>69</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="5">
         <v>69</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="5">
         <v>74</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="N3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="P3" s="13" t="s">
+      <c r="O3" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="S3" s="10" t="s">
         <v>17</v>
       </c>
       <c r="T3" t="s">
@@ -1540,31 +2089,31 @@
       <c r="C4" s="4">
         <v>56</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="13" t="s">
+      <c r="E4" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="5">
         <v>43</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="5">
         <v>64</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="5">
         <v>65</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="13" t="s">
+      <c r="L4" s="19" t="s">
         <v>4</v>
       </c>
       <c r="M4" s="4" t="s">
@@ -1579,7 +2128,7 @@
       <c r="P4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="S4" s="8" t="s">
+      <c r="S4" s="11" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1620,83 +2169,88 @@
       <c r="L5" s="4">
         <v>65</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="M5" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="O5" s="4">
+      <c r="N5" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="O5" s="5">
         <v>12</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="S5" s="9" t="s">
+      <c r="S5" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:21">
+      <c r="A6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="5">
         <v>63</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="5">
         <v>61</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="5">
         <v>56</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="5">
         <v>61</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="5">
         <v>72</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="5">
         <v>69</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="5">
         <v>61</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="5">
         <v>62</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="5">
         <v>65</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6" s="5">
         <v>54</v>
       </c>
-      <c r="N6" s="4">
+      <c r="N6" s="5">
         <v>61</v>
       </c>
-      <c r="O6" s="4">
+      <c r="O6" s="5">
         <v>62</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="P6" s="5" t="s">
         <v>24</v>
+      </c>
+      <c r="S6" s="13"/>
+      <c r="T6" s="14"/>
+      <c r="U6" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="4">
+      <c r="A7" s="5">
         <v>65</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="13" t="s">
+      <c r="C7" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="19" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="4">
@@ -1711,95 +2265,95 @@
       <c r="H7" s="4">
         <v>73</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="K7" s="4">
+      <c r="J7" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="K7" s="5">
         <v>17</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M7" s="4">
+      <c r="M7" s="5">
         <v>70</v>
       </c>
-      <c r="N7" s="4">
+      <c r="N7" s="5">
         <v>61</v>
       </c>
-      <c r="O7" s="4">
+      <c r="O7" s="5">
         <v>72</v>
       </c>
-      <c r="P7" s="4">
+      <c r="P7" s="5">
         <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="4">
+      <c r="A8" s="5">
         <v>30</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="5">
         <v>32</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="C8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="5">
         <v>63</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="5">
         <v>68</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="5">
         <v>61</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="5">
         <v>70</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="5">
         <v>74</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="5">
         <v>65</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="5">
         <v>72</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="5">
         <v>30</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="5">
         <v>31</v>
       </c>
-      <c r="M8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N8" s="4">
+      <c r="M8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" s="5">
         <v>44</v>
       </c>
-      <c r="O8" s="4">
+      <c r="O8" s="5">
         <v>65</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="P8" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="13" t="s">
+      <c r="B9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="13" t="s">
+      <c r="D9" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="19" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="4">
@@ -1811,28 +2365,28 @@
       <c r="H9" s="4">
         <v>64</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="13" t="s">
+      <c r="J9" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9" s="5">
         <v>28</v>
       </c>
-      <c r="M9" s="4">
+      <c r="M9" s="5">
         <v>29</v>
       </c>
-      <c r="N9" s="4">
+      <c r="N9" s="5">
         <v>49</v>
       </c>
-      <c r="O9" s="13" t="s">
+      <c r="O9" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="P9" s="13" t="s">
+      <c r="P9" s="19" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1870,80 +2424,80 @@
       <c r="K10" s="4">
         <v>65</v>
       </c>
-      <c r="L10" s="13" t="s">
+      <c r="L10" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="M10" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="N10" s="13" t="s">
+      <c r="M10" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="O10" s="4">
+      <c r="O10" s="5">
         <v>44</v>
       </c>
-      <c r="P10" s="4">
+      <c r="P10" s="5">
         <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="4">
+      <c r="D11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="5">
         <v>61</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="5">
         <v>76</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="5">
         <v>61</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="J11" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="13" t="s">
+      <c r="K11" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="M11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="N11" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="O11" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="P11" s="13" t="s">
+      <c r="N11" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="O11" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P11" s="18" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="19" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="4">
@@ -1968,7 +2522,7 @@
         <v>32</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L12" s="4">
         <v>63</v>
@@ -2000,7 +2554,7 @@
         <v>31</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F13" s="4">
         <v>44</v>
@@ -2014,617 +2568,617 @@
       <c r="I13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="L13" s="4">
+      <c r="K13" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="L13" s="5">
         <v>10</v>
       </c>
-      <c r="M13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N13" s="4">
+      <c r="M13" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="N13" s="5">
         <v>61</v>
       </c>
-      <c r="O13" s="4">
+      <c r="O13" s="5">
         <v>76</v>
       </c>
-      <c r="P13" s="4">
+      <c r="P13" s="5">
         <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="A14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <v>61</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="5">
         <v>67</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" s="4">
+      <c r="F14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="5">
         <v>62</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J14" s="4">
+      <c r="I14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14" s="5">
         <v>65</v>
       </c>
-      <c r="K14" s="4">
+      <c r="K14" s="5">
         <v>63</v>
       </c>
-      <c r="L14" s="4">
+      <c r="L14" s="8">
         <v>74</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="4">
+      <c r="M14" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="6">
         <v>21</v>
       </c>
-      <c r="O14" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" s="13" t="s">
+      <c r="O14" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="20" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="13" t="s">
+      <c r="A15" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="13" t="s">
+      <c r="C15" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="13" t="s">
+      <c r="G15" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="L15" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="M15" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="13" t="s">
-        <v>34</v>
+      <c r="M15" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="20" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="13" t="s">
+      <c r="A16" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="13" t="s">
+      <c r="C16" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="13" t="s">
+      <c r="E16" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="I16" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="J16" s="13" t="s">
+      <c r="I16" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="J16" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="K16" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="L16" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="M16" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="N16" s="4">
+      <c r="K16" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="L16" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="M16" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="N16" s="6">
         <v>38</v>
       </c>
-      <c r="O16" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="P16" s="13" t="s">
-        <v>34</v>
+      <c r="O16" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="P16" s="20" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="13" t="s">
+      <c r="A17" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="4" t="s">
+      <c r="C17" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="N17" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="N17" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="O17" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>38</v>
+      <c r="P17" s="6" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="4" t="s">
+      <c r="A18" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="4" t="s">
+      <c r="G18" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="K18" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="M18" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="4" t="s">
-        <v>39</v>
+      <c r="K18" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="M18" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="6" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="13" t="s">
+      <c r="A19" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="4">
+      <c r="C19" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="6">
         <v>10</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K19" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="L19" s="13" t="s">
+      <c r="E19" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="L19" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M19" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="N19" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="O19" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="P19" s="4" t="s">
+      <c r="M19" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="N19" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="O19" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="P19" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="13" t="s">
+      <c r="A20" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="I20" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K20" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="L20" s="4" t="s">
+      <c r="I20" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M20" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="13" t="s">
+      <c r="M20" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="O20" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="13" t="s">
+      <c r="O20" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="13" t="s">
+      <c r="A21" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="G21" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="13" t="s">
+      <c r="G21" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="I21" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="L21" s="4" t="s">
+      <c r="I21" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M21" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="O21" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="P21" s="13" t="s">
+      <c r="M21" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="O21" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="P21" s="20" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="4">
+      <c r="A22" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="6">
         <v>60</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="D22" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="K22" s="4" t="s">
+      <c r="G22" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="L22" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="O22" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="P22" s="13" t="s">
+      <c r="I22" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="P22" s="20" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="4" t="s">
+      <c r="B23" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F23" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="K23" s="4">
+      <c r="F23" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="6">
         <v>13</v>
       </c>
-      <c r="L23" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="M23" s="4" t="s">
+      <c r="L23" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="N23" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="O23" s="4">
+      <c r="N23" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="6">
         <v>14</v>
       </c>
-      <c r="P23" s="13" t="s">
+      <c r="P23" s="20" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="13" t="s">
+      <c r="A24" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="H24" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="4" t="s">
+      <c r="H24" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="K24" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="L24" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="M24" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="N24" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="O24" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="P24" s="13" t="s">
+      <c r="L24" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="N24" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="P24" s="20" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="13" t="s">
+      <c r="A25" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" s="4">
+      <c r="D25" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="6">
         <v>10</v>
       </c>
-      <c r="F25" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J25" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="K25" s="4">
+      <c r="F25" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="I25" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="K25" s="6">
         <v>11</v>
       </c>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2632,5 +3186,6 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/byteCodeDemo.xlsx
+++ b/byteCodeDemo.xlsx
@@ -508,7 +508,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="48">
   <si>
     <t>CA</t>
   </si>
@@ -588,7 +588,10 @@
     <t>常量池计数器</t>
   </si>
   <si>
-    <t>这两个颜色交替表示常量池表中内容</t>
+    <t>常量池表数据1</t>
+  </si>
+  <si>
+    <t>常量池表数据2</t>
   </si>
   <si>
     <t>2F</t>
@@ -613,6 +616,9 @@
   </si>
   <si>
     <t>4F</t>
+  </si>
+  <si>
+    <t>访问标识</t>
   </si>
   <si>
     <t>02</t>
@@ -818,18 +824,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -869,6 +875,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1173,10 +1185,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1185,16 +1197,16 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1206,10 +1218,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1230,28 +1242,28 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1260,19 +1272,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1284,38 +1293,41 @@
     <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1343,6 +1355,9 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1359,6 +1374,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
@@ -1374,6 +1392,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
@@ -1912,11 +1933,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:T25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="19" max="19" width="24.125" customWidth="1"/>
-    <col min="20" max="20" width="14.5" customWidth="1"/>
+    <col min="20" max="20" width="25.375" customWidth="1"/>
     <col min="21" max="21" width="31.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1933,19 +1954,19 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="16" t="s">
+      <c r="E1" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="18" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="3">
         <v>34</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="19" t="s">
         <v>4</v>
       </c>
       <c r="J1" s="7">
@@ -1954,60 +1975,60 @@
       <c r="K1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="18" t="s">
+      <c r="L1" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="N1" s="20" t="s">
         <v>4</v>
       </c>
       <c r="O1" s="5">
         <v>12</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="21" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="19" t="s">
+      <c r="A2" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="21" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="4">
         <v>13</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="20" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="5">
         <v>14</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="21" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="4">
         <v>15</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="K2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="M2" s="18" t="s">
+      <c r="L2" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="20" t="s">
         <v>8</v>
       </c>
       <c r="N2" s="5" t="s">
@@ -2019,30 +2040,30 @@
       <c r="P2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="9" t="s">
+      <c r="S2" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="19" t="s">
+      <c r="B3" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="21" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="4">
         <v>49</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="18" t="s">
+      <c r="F3" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="20" t="s">
         <v>14</v>
       </c>
       <c r="H3" s="5" t="s">
@@ -2063,16 +2084,16 @@
       <c r="M3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="19" t="s">
+      <c r="N3" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="P3" s="19" t="s">
+      <c r="O3" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="S3" s="10" t="s">
+      <c r="S3" s="11" t="s">
         <v>17</v>
       </c>
       <c r="T3" t="s">
@@ -2089,13 +2110,13 @@
       <c r="C4" s="4">
         <v>56</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="18" t="s">
+      <c r="E4" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="20" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="5">
@@ -2110,10 +2131,10 @@
       <c r="J4" s="5">
         <v>65</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="19" t="s">
+      <c r="L4" s="21" t="s">
         <v>4</v>
       </c>
       <c r="M4" s="4" t="s">
@@ -2128,7 +2149,7 @@
       <c r="P4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="S4" s="11" t="s">
+      <c r="S4" s="12" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2169,10 +2190,10 @@
       <c r="L5" s="4">
         <v>65</v>
       </c>
-      <c r="M5" s="18" t="s">
+      <c r="M5" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="18" t="s">
+      <c r="N5" s="20" t="s">
         <v>4</v>
       </c>
       <c r="O5" s="5">
@@ -2181,11 +2202,11 @@
       <c r="P5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="S5" s="12" t="s">
+      <c r="S5" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:20">
       <c r="A6" s="5" t="s">
         <v>19</v>
       </c>
@@ -2234,23 +2255,24 @@
       <c r="P6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="14"/>
-      <c r="U6" t="s">
+      <c r="S6" s="14" t="s">
         <v>26</v>
+      </c>
+      <c r="T6" s="15" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="5">
         <v>65</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="19" t="s">
+      <c r="C7" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="4">
@@ -2265,10 +2287,10 @@
       <c r="H7" s="4">
         <v>73</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="18" t="s">
+      <c r="J7" s="20" t="s">
         <v>4</v>
       </c>
       <c r="K7" s="5">
@@ -2298,7 +2320,7 @@
         <v>32</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" s="5">
         <v>63</v>
@@ -2328,7 +2350,7 @@
         <v>31</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N8" s="5">
         <v>44</v>
@@ -2345,15 +2367,15 @@
         <v>19</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="19" t="s">
+      <c r="D9" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="21" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="4">
@@ -2365,13 +2387,13 @@
       <c r="H9" s="4">
         <v>64</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="18" t="s">
+      <c r="J9" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="20" t="s">
         <v>8</v>
       </c>
       <c r="L9" s="5">
@@ -2383,10 +2405,10 @@
       <c r="N9" s="5">
         <v>49</v>
       </c>
-      <c r="O9" s="19" t="s">
+      <c r="O9" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="P9" s="19" t="s">
+      <c r="P9" s="21" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2424,13 +2446,13 @@
       <c r="K10" s="4">
         <v>65</v>
       </c>
-      <c r="L10" s="18" t="s">
+      <c r="L10" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M10" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="N10" s="18" t="s">
+      <c r="M10" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="20" t="s">
         <v>7</v>
       </c>
       <c r="O10" s="5">
@@ -2448,10 +2470,10 @@
         <v>19</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11" s="5">
         <v>61</v>
@@ -2463,41 +2485,41 @@
         <v>61</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="J11" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="19" t="s">
+      <c r="K11" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="M11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="M11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="N11" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="O11" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P11" s="18" t="s">
+      <c r="N11" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="O11" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="P11" s="20" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="21" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="4">
@@ -2522,7 +2544,7 @@
         <v>32</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L12" s="4">
         <v>63</v>
@@ -2554,7 +2576,7 @@
         <v>31</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F13" s="4">
         <v>44</v>
@@ -2568,17 +2590,17 @@
       <c r="I13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="18" t="s">
+      <c r="J13" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="18" t="s">
+      <c r="K13" s="20" t="s">
         <v>4</v>
       </c>
       <c r="L13" s="5">
         <v>10</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N13" s="5">
         <v>61</v>
@@ -2590,9 +2612,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:19">
       <c r="A14" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>24</v>
@@ -2607,16 +2629,16 @@
         <v>67</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H14" s="5">
         <v>62</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J14" s="5">
         <v>65</v>
@@ -2627,263 +2649,266 @@
       <c r="L14" s="8">
         <v>74</v>
       </c>
-      <c r="M14" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="6">
+      <c r="M14" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="9">
         <v>21</v>
       </c>
-      <c r="O14" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" s="20" t="s">
+      <c r="O14" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="23" t="s">
         <v>8</v>
+      </c>
+      <c r="S14" s="16" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="20" t="s">
+      <c r="A15" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="20" t="s">
+      <c r="C15" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="K15" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="20" t="s">
+      <c r="G15" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="K15" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="L15" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="M15" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="20" t="s">
-        <v>35</v>
+      <c r="M15" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="23" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="20" t="s">
+      <c r="A16" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="20" t="s">
+      <c r="C16" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="20" t="s">
+      <c r="E16" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="I16" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="J16" s="20" t="s">
+      <c r="I16" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J16" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="K16" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="L16" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="M16" s="20" t="s">
+      <c r="K16" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="L16" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="M16" s="23" t="s">
         <v>4</v>
       </c>
       <c r="N16" s="6">
         <v>38</v>
       </c>
-      <c r="O16" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="P16" s="20" t="s">
-        <v>35</v>
+      <c r="O16" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="P16" s="23" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="20" t="s">
+      <c r="A17" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="20" t="s">
+      <c r="C17" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="23" t="s">
         <v>4</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>5</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I17" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L17" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N17" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="I17" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L17" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="M17" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="N17" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="O17" s="20" t="s">
-        <v>35</v>
-      </c>
       <c r="P17" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="20" t="s">
+      <c r="A18" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="23" t="s">
         <v>4</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="20" t="s">
+      <c r="G18" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="23" t="s">
         <v>4</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="K18" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="M18" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="20" t="s">
+      <c r="K18" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="M18" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="23" t="s">
         <v>4</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="20" t="s">
+      <c r="A19" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="23" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="6">
         <v>10</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="E19" s="23" t="s">
         <v>4</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G19" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="H19" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="I19" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="23" t="s">
         <v>4</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="K19" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="L19" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="L19" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="M19" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="N19" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="O19" s="20" t="s">
+      <c r="M19" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="N19" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="O19" s="23" t="s">
         <v>4</v>
       </c>
       <c r="P19" s="6" t="s">
@@ -2891,152 +2916,152 @@
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="23" t="s">
         <v>4</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="23" t="s">
         <v>4</v>
       </c>
       <c r="D20" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="I20" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K20" s="20" t="s">
+      <c r="K20" s="23" t="s">
         <v>4</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M20" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="20" t="s">
+      <c r="M20" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="O20" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="20" t="s">
+      <c r="O20" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="23" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="20" t="s">
+      <c r="A21" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="23" t="s">
         <v>4</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="G21" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="20" t="s">
+      <c r="G21" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="I21" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="20" t="s">
+      <c r="I21" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="23" t="s">
         <v>4</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>20</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="P21" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="P21" s="23" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>33</v>
+      <c r="A22" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>34</v>
       </c>
       <c r="C22" s="6">
         <v>60</v>
       </c>
       <c r="D22" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>36</v>
-      </c>
       <c r="H22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I22" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="20" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="I22" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="L22" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="O22" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="P22" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="L22" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="P22" s="23" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3044,131 +3069,131 @@
       <c r="A23" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="20" t="s">
+      <c r="B23" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="23" t="s">
         <v>4</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F23" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="H23" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="I23" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="J23" s="20" t="s">
+      <c r="F23" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="23" t="s">
         <v>4</v>
       </c>
       <c r="K23" s="6">
         <v>13</v>
       </c>
-      <c r="L23" s="20" t="s">
+      <c r="L23" s="23" t="s">
         <v>4</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="N23" s="20" t="s">
+      <c r="N23" s="23" t="s">
         <v>4</v>
       </c>
       <c r="O23" s="6">
         <v>14</v>
       </c>
-      <c r="P23" s="20" t="s">
+      <c r="P23" s="23" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:16">
       <c r="A24" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="23" t="s">
         <v>4</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="H24" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="20" t="s">
+      <c r="H24" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="23" t="s">
         <v>4</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="L24" s="20" t="s">
+      <c r="L24" s="23" t="s">
         <v>4</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="N24" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="N24" s="23" t="s">
         <v>4</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="P24" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="P24" s="23" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="20" t="s">
+      <c r="A25" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="23" t="s">
         <v>4</v>
       </c>
       <c r="E25" s="6">
         <v>10</v>
       </c>
-      <c r="F25" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="H25" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="I25" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="J25" s="20" t="s">
+      <c r="F25" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="I25" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="J25" s="23" t="s">
         <v>4</v>
       </c>
       <c r="K25" s="6">

--- a/byteCodeDemo.xlsx
+++ b/byteCodeDemo.xlsx
@@ -508,7 +508,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="51">
   <si>
     <t>CA</t>
   </si>
@@ -624,6 +624,12 @@
     <t>02</t>
   </si>
   <si>
+    <t>当前类索引</t>
+  </si>
+  <si>
+    <t>父类索引</t>
+  </si>
+  <si>
     <t>2A</t>
   </si>
   <si>
@@ -634,6 +640,9 @@
   </si>
   <si>
     <t>B1</t>
+  </si>
+  <si>
+    <t>接口计数器</t>
   </si>
   <si>
     <t>0E</t>
@@ -824,18 +833,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -881,6 +890,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1185,10 +1200,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1197,16 +1212,16 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1218,10 +1233,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1242,28 +1257,28 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1272,19 +1287,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1296,38 +1308,41 @@
     <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1379,6 +1394,9 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1395,6 +1413,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
@@ -1954,19 +1975,19 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="18" t="s">
+      <c r="E1" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="19" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="3">
         <v>34</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="20" t="s">
         <v>4</v>
       </c>
       <c r="J1" s="7">
@@ -1975,60 +1996,60 @@
       <c r="K1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="20" t="s">
+      <c r="L1" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="N1" s="21" t="s">
         <v>4</v>
       </c>
       <c r="O1" s="5">
         <v>12</v>
       </c>
-      <c r="P1" s="21" t="s">
+      <c r="P1" s="22" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="21" t="s">
+      <c r="A2" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="22" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="4">
         <v>13</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="5">
         <v>14</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="22" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="4">
         <v>15</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="M2" s="20" t="s">
+      <c r="L2" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="21" t="s">
         <v>8</v>
       </c>
       <c r="N2" s="5" t="s">
@@ -2045,25 +2066,25 @@
       </c>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="21" t="s">
+      <c r="B3" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="22" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="4">
         <v>49</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="20" t="s">
+      <c r="F3" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="21" t="s">
         <v>14</v>
       </c>
       <c r="H3" s="5" t="s">
@@ -2084,13 +2105,13 @@
       <c r="M3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="21" t="s">
+      <c r="N3" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="P3" s="21" t="s">
+      <c r="O3" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="22" t="s">
         <v>8</v>
       </c>
       <c r="S3" s="11" t="s">
@@ -2110,13 +2131,13 @@
       <c r="C4" s="4">
         <v>56</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="20" t="s">
+      <c r="E4" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="21" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="5">
@@ -2131,10 +2152,10 @@
       <c r="J4" s="5">
         <v>65</v>
       </c>
-      <c r="K4" s="21" t="s">
+      <c r="K4" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="21" t="s">
+      <c r="L4" s="22" t="s">
         <v>4</v>
       </c>
       <c r="M4" s="4" t="s">
@@ -2190,10 +2211,10 @@
       <c r="L5" s="4">
         <v>65</v>
       </c>
-      <c r="M5" s="20" t="s">
+      <c r="M5" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="20" t="s">
+      <c r="N5" s="21" t="s">
         <v>4</v>
       </c>
       <c r="O5" s="5">
@@ -2266,13 +2287,13 @@
       <c r="A7" s="5">
         <v>65</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="21" t="s">
+      <c r="C7" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="4">
@@ -2287,10 +2308,10 @@
       <c r="H7" s="4">
         <v>73</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="20" t="s">
+      <c r="J7" s="21" t="s">
         <v>4</v>
       </c>
       <c r="K7" s="5">
@@ -2369,13 +2390,13 @@
       <c r="B9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="21" t="s">
+      <c r="D9" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="22" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="4">
@@ -2387,13 +2408,13 @@
       <c r="H9" s="4">
         <v>64</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="20" t="s">
+      <c r="J9" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="21" t="s">
         <v>8</v>
       </c>
       <c r="L9" s="5">
@@ -2405,10 +2426,10 @@
       <c r="N9" s="5">
         <v>49</v>
       </c>
-      <c r="O9" s="21" t="s">
+      <c r="O9" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="P9" s="21" t="s">
+      <c r="P9" s="22" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2446,13 +2467,13 @@
       <c r="K10" s="4">
         <v>65</v>
       </c>
-      <c r="L10" s="20" t="s">
+      <c r="L10" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="M10" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="N10" s="20" t="s">
+      <c r="M10" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="21" t="s">
         <v>7</v>
       </c>
       <c r="O10" s="5">
@@ -2487,39 +2508,39 @@
       <c r="H11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="J11" s="21" t="s">
+      <c r="I11" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="21" t="s">
+      <c r="K11" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" s="22" t="s">
         <v>33</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="O11" s="20" t="s">
+      <c r="N11" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="O11" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="P11" s="20" t="s">
+      <c r="P11" s="21" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="22" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="4">
@@ -2590,10 +2611,10 @@
       <c r="I13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="20" t="s">
+      <c r="J13" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="20" t="s">
+      <c r="K13" s="21" t="s">
         <v>4</v>
       </c>
       <c r="L13" s="5">
@@ -2649,266 +2670,276 @@
       <c r="L14" s="8">
         <v>74</v>
       </c>
-      <c r="M14" s="22" t="s">
+      <c r="M14" s="23" t="s">
         <v>4</v>
       </c>
       <c r="N14" s="9">
         <v>21</v>
       </c>
-      <c r="O14" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" s="23" t="s">
+      <c r="O14" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="19" t="s">
         <v>8</v>
       </c>
       <c r="S14" s="16" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
-      <c r="A15" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="23" t="s">
+    <row r="15" spans="1:20">
+      <c r="A15" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="23" t="s">
+      <c r="C15" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="23" t="s">
+      <c r="G15" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="I15" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="23" t="s">
+      <c r="I15" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="K15" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="23" t="s">
+      <c r="K15" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="L15" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="M15" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="23" t="s">
+      <c r="M15" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="25" t="s">
         <v>37</v>
       </c>
+      <c r="S15" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="T15" s="17"/>
     </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="23" t="s">
+    <row r="16" spans="1:19">
+      <c r="A16" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="23" t="s">
+      <c r="C16" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="23" t="s">
+      <c r="E16" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="G16" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="23" t="s">
+      <c r="G16" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="I16" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J16" s="23" t="s">
+      <c r="I16" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="J16" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="K16" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="L16" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="M16" s="23" t="s">
+      <c r="K16" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="L16" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="M16" s="25" t="s">
         <v>4</v>
       </c>
       <c r="N16" s="6">
         <v>38</v>
       </c>
-      <c r="O16" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="P16" s="23" t="s">
+      <c r="O16" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="P16" s="25" t="s">
         <v>37</v>
       </c>
+      <c r="S16" s="14" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="17" spans="1:16">
-      <c r="A17" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="23" t="s">
+    <row r="17" spans="1:19">
+      <c r="A17" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="23" t="s">
+      <c r="C17" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="25" t="s">
         <v>4</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>5</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I17" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="I17" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="25" t="s">
         <v>10</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="L17" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="L17" s="25" t="s">
         <v>6</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="N17" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O17" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="N17" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="25" t="s">
         <v>37</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+      <c r="S17" s="10" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="23" t="s">
+      <c r="A18" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="25" t="s">
         <v>4</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="23" t="s">
+      <c r="G18" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="25" t="s">
         <v>4</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="K18" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="23" t="s">
+      <c r="K18" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="M18" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="23" t="s">
+      <c r="M18" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="25" t="s">
         <v>4</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="23" t="s">
+      <c r="A19" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="6">
         <v>10</v>
       </c>
-      <c r="E19" s="23" t="s">
+      <c r="E19" s="25" t="s">
         <v>4</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H19" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I19" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="25" t="s">
         <v>4</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="K19" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="L19" s="23" t="s">
+      <c r="K19" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="L19" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="M19" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="N19" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O19" s="23" t="s">
+      <c r="M19" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="N19" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="O19" s="25" t="s">
         <v>4</v>
       </c>
       <c r="P19" s="6" t="s">
@@ -2916,152 +2947,152 @@
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="25" t="s">
         <v>4</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="I20" s="23" t="s">
+      <c r="I20" s="25" t="s">
         <v>4</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K20" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="K20" s="25" t="s">
         <v>4</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M20" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="23" t="s">
+      <c r="M20" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="O20" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="23" t="s">
+      <c r="O20" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="25" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="23" t="s">
+      <c r="A21" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="25" t="s">
         <v>4</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="G21" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="23" t="s">
+      <c r="G21" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="I21" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="23" t="s">
+      <c r="I21" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="25" t="s">
         <v>4</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>20</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="P21" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="P21" s="25" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="25" t="s">
         <v>34</v>
       </c>
       <c r="C22" s="6">
         <v>60</v>
       </c>
       <c r="D22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="23" t="s">
+      <c r="H22" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I22" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="G22" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="I22" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="23" t="s">
+      <c r="K22" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L22" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="K22" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="L22" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O22" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="P22" s="23" t="s">
+      <c r="P22" s="25" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3069,131 +3100,131 @@
       <c r="A23" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="23" t="s">
+      <c r="B23" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="25" t="s">
         <v>4</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F23" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G23" s="23" t="s">
+      <c r="F23" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="H23" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I23" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J23" s="23" t="s">
+      <c r="H23" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="25" t="s">
         <v>4</v>
       </c>
       <c r="K23" s="6">
         <v>13</v>
       </c>
-      <c r="L23" s="23" t="s">
+      <c r="L23" s="25" t="s">
         <v>4</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="N23" s="23" t="s">
+      <c r="N23" s="25" t="s">
         <v>4</v>
       </c>
       <c r="O23" s="6">
         <v>14</v>
       </c>
-      <c r="P23" s="23" t="s">
+      <c r="P23" s="25" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:16">
       <c r="A24" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="25" t="s">
         <v>4</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="23" t="s">
+      <c r="F24" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="H24" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="23" t="s">
+      <c r="H24" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="25" t="s">
         <v>4</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="L24" s="23" t="s">
+      <c r="L24" s="25" t="s">
         <v>4</v>
       </c>
       <c r="M24" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="N24" s="23" t="s">
+      <c r="N24" s="25" t="s">
         <v>4</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="P24" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="P24" s="25" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="23" t="s">
+      <c r="A25" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="23" t="s">
+      <c r="D25" s="25" t="s">
         <v>4</v>
       </c>
       <c r="E25" s="6">
         <v>10</v>
       </c>
-      <c r="F25" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="H25" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I25" s="23" t="s">
+      <c r="F25" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="I25" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="J25" s="23" t="s">
+      <c r="J25" s="25" t="s">
         <v>4</v>
       </c>
       <c r="K25" s="6">

--- a/byteCodeDemo.xlsx
+++ b/byteCodeDemo.xlsx
@@ -1,15 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12540"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="byteCodeDemo" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -508,7 +521,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="52">
   <si>
     <t>CA</t>
   </si>
@@ -642,10 +655,13 @@
     <t>B1</t>
   </si>
   <si>
-    <t>接口计数器</t>
+    <t>实现的接口计数器</t>
   </si>
   <si>
     <t>0E</t>
+  </si>
+  <si>
+    <t>字段计数器</t>
   </si>
   <si>
     <t>0B</t>
@@ -666,7 +682,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -689,34 +705,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -730,14 +718,6 @@
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -777,6 +757,21 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -827,15 +822,31 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -843,8 +854,13 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="41">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -871,79 +887,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -955,121 +1061,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1092,21 +1114,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1139,6 +1146,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1197,152 +1219,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1361,37 +1383,43 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
@@ -1403,19 +1431,22 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
@@ -1424,52 +1455,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1666,7 +1697,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1675,7 +1706,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1962,7 +1993,7 @@
     <col min="21" max="21" width="31.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1975,81 +2006,81 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="19" t="s">
+      <c r="E1" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="21" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="3">
         <v>34</v>
       </c>
-      <c r="I1" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="7">
+      <c r="I1" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="4">
         <v>16</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="21" t="s">
+      <c r="L1" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="N1" s="23" t="s">
         <v>4</v>
       </c>
       <c r="O1" s="5">
         <v>12</v>
       </c>
-      <c r="P1" s="22" t="s">
+      <c r="P1" s="24" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
-      <c r="A2" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="22" t="s">
+    <row r="2" spans="1:20">
+      <c r="A2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="4">
+      <c r="C2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="6">
         <v>13</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="23" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="5">
         <v>14</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="J2" s="4">
+      <c r="I2" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="6">
         <v>15</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="M2" s="21" t="s">
+      <c r="L2" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="23" t="s">
         <v>8</v>
       </c>
       <c r="N2" s="5" t="s">
@@ -2061,30 +2092,30 @@
       <c r="P2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="S2" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="22" t="s">
+      <c r="B3" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="6">
         <v>49</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="21" t="s">
+      <c r="F3" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="23" t="s">
         <v>14</v>
       </c>
       <c r="H3" s="5" t="s">
@@ -2105,39 +2136,39 @@
       <c r="M3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="22" t="s">
+      <c r="N3" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="P3" s="22" t="s">
+      <c r="O3" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="S3" s="11" t="s">
+      <c r="S3" s="8" t="s">
         <v>17</v>
       </c>
       <c r="T3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
-      <c r="A4" s="4">
+    <row r="4" spans="1:20">
+      <c r="A4" s="6">
         <v>28</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="6">
         <v>29</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="6">
         <v>56</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="21" t="s">
+      <c r="E4" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="23" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="5">
@@ -2152,69 +2183,69 @@
       <c r="J4" s="5">
         <v>65</v>
       </c>
-      <c r="K4" s="22" t="s">
+      <c r="K4" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="M4" s="4" t="s">
+      <c r="L4" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="M4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O4" s="4">
+      <c r="O4" s="6">
         <v>69</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="P4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="S4" s="12" t="s">
+      <c r="S4" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
-      <c r="A5" s="4">
+    <row r="5" spans="1:20">
+      <c r="A5" s="6">
         <v>65</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="6">
         <v>75</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="6">
         <v>62</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="6">
         <v>65</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="6">
         <v>72</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="6">
         <v>54</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="6">
         <v>61</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="6">
         <v>62</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="6">
         <v>65</v>
       </c>
-      <c r="M5" s="21" t="s">
+      <c r="M5" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="21" t="s">
+      <c r="N5" s="23" t="s">
         <v>4</v>
       </c>
       <c r="O5" s="5">
@@ -2223,7 +2254,7 @@
       <c r="P5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="S5" s="13" t="s">
+      <c r="S5" s="10" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2276,42 +2307,42 @@
       <c r="P6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="S6" s="14" t="s">
+      <c r="S6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="T6" s="15" t="s">
+      <c r="T6" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:20">
       <c r="A7" s="5">
         <v>65</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="22" t="s">
+      <c r="C7" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="6">
         <v>74</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="6">
         <v>68</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="6">
         <v>69</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="6">
         <v>73</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="J7" s="23" t="s">
         <v>4</v>
       </c>
       <c r="K7" s="5">
@@ -2333,7 +2364,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:20">
       <c r="A8" s="5">
         <v>30</v>
       </c>
@@ -2383,38 +2414,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:20">
       <c r="A9" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="22" t="s">
+      <c r="D9" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="6">
         <v>61</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="6">
         <v>64</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="6">
         <v>64</v>
       </c>
-      <c r="I9" s="21" t="s">
+      <c r="I9" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="21" t="s">
+      <c r="J9" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="23" t="s">
         <v>8</v>
       </c>
       <c r="L9" s="5">
@@ -2426,54 +2457,54 @@
       <c r="N9" s="5">
         <v>49</v>
       </c>
-      <c r="O9" s="22" t="s">
+      <c r="O9" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="P9" s="22" t="s">
+      <c r="P9" s="24" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:20">
+      <c r="A10" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="6">
         <v>53</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="6">
         <v>75</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="6">
         <v>72</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="6">
         <v>63</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="6">
         <v>65</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="6">
         <v>46</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="6">
         <v>69</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10" s="6">
         <v>65</v>
       </c>
-      <c r="L10" s="21" t="s">
+      <c r="L10" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="M10" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="N10" s="21" t="s">
+      <c r="M10" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="23" t="s">
         <v>7</v>
       </c>
       <c r="O10" s="5">
@@ -2483,7 +2514,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:20">
       <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
@@ -2505,116 +2536,116 @@
       <c r="G11" s="5">
         <v>61</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="J11" s="22" t="s">
+      <c r="I11" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="22" t="s">
+      <c r="K11" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" s="24" t="s">
         <v>33</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="O11" s="21" t="s">
+      <c r="N11" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="O11" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="P11" s="21" t="s">
+      <c r="P11" s="23" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
-      <c r="A12" s="21" t="s">
+    <row r="12" spans="1:20">
+      <c r="A12" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="4">
+      <c r="C12" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="6">
         <v>15</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="6">
         <v>70</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="6">
         <v>61</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="6">
         <v>72</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="6">
         <v>74</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="6">
         <v>30</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="6">
         <v>32</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="L12" s="4">
+      <c r="L12" s="6">
         <v>63</v>
       </c>
-      <c r="M12" s="4">
+      <c r="M12" s="6">
         <v>68</v>
       </c>
-      <c r="N12" s="4">
+      <c r="N12" s="6">
         <v>61</v>
       </c>
-      <c r="O12" s="4">
+      <c r="O12" s="6">
         <v>70</v>
       </c>
-      <c r="P12" s="4">
+      <c r="P12" s="6">
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
-      <c r="A13" s="4">
+    <row r="13" spans="1:20">
+      <c r="A13" s="6">
         <v>65</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="6">
         <v>72</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="6">
         <v>30</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="6">
         <v>31</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="6">
         <v>44</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="6">
         <v>65</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="21" t="s">
+      <c r="J13" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="21" t="s">
+      <c r="K13" s="23" t="s">
         <v>4</v>
       </c>
       <c r="L13" s="5">
@@ -2633,7 +2664,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:20">
       <c r="A14" s="5" t="s">
         <v>28</v>
       </c>
@@ -2667,574 +2698,577 @@
       <c r="K14" s="5">
         <v>63</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="13">
         <v>74</v>
       </c>
-      <c r="M14" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="9">
+      <c r="M14" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="N14" s="14">
         <v>21</v>
       </c>
-      <c r="O14" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" s="19" t="s">
+      <c r="O14" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="16" t="s">
+      <c r="S14" s="15" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:20">
-      <c r="A15" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="22" t="s">
+      <c r="A15" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="25" t="s">
+      <c r="C15" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="25" t="s">
+      <c r="G15" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="I15" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="25" t="s">
+      <c r="I15" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="K15" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="25" t="s">
+      <c r="K15" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="L15" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="M15" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="25" t="s">
+      <c r="M15" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="S15" s="12" t="s">
+      <c r="S15" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="T15" s="17"/>
+      <c r="T15" s="18"/>
     </row>
-    <row r="16" spans="1:19">
-      <c r="A16" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="25" t="s">
+    <row r="16" spans="1:20">
+      <c r="A16" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="25" t="s">
+      <c r="C16" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="25" t="s">
+      <c r="E16" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="G16" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="25" t="s">
+      <c r="G16" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="I16" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="J16" s="25" t="s">
+      <c r="I16" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="J16" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="K16" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="L16" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="M16" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="N16" s="6">
+      <c r="K16" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="L16" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="M16" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="N16" s="17">
         <v>38</v>
       </c>
-      <c r="O16" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="P16" s="25" t="s">
+      <c r="O16" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="P16" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="S16" s="14" t="s">
+      <c r="S16" s="11" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="25" t="s">
+      <c r="A17" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="6" t="s">
+      <c r="C17" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="I17" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="25" t="s">
+      <c r="I17" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="K17" s="6" t="s">
+      <c r="K17" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="L17" s="25" t="s">
+      <c r="L17" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="M17" s="6" t="s">
+      <c r="M17" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="N17" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="O17" s="25" t="s">
+      <c r="N17" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="P17" s="6" t="s">
+      <c r="P17" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="S17" s="10" t="s">
+      <c r="S17" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="25" t="s">
+    <row r="18" spans="1:19">
+      <c r="A18" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="6" t="s">
+      <c r="E18" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="6" t="s">
+      <c r="G18" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="K18" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="25" t="s">
+      <c r="K18" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="M18" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="6" t="s">
+      <c r="M18" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="17" t="s">
         <v>45</v>
       </c>
+      <c r="S18" s="19" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="19" spans="1:16">
-      <c r="A19" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="25" t="s">
+    <row r="19" spans="1:19">
+      <c r="A19" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="17">
         <v>10</v>
       </c>
-      <c r="E19" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G19" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="H19" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="I19" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="J19" s="6" t="s">
+      <c r="E19" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="J19" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="K19" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="L19" s="25" t="s">
+      <c r="K19" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="L19" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="M19" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="N19" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="O19" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="P19" s="6" t="s">
+      <c r="M19" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="N19" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="O19" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="P19" s="17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
-      <c r="A20" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="6" t="s">
+    <row r="20" spans="1:19">
+      <c r="A20" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="6" t="s">
+      <c r="C20" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K20" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M20" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="O20" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="A21" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="M21" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="O21" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="P21" s="28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="17">
+        <v>60</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="H22" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="I22" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="L22" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="P22" s="28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="17">
+        <v>13</v>
+      </c>
+      <c r="L23" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="17">
+        <v>14</v>
+      </c>
+      <c r="P23" s="28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
+      <c r="A24" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="E20" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="25" t="s">
+      <c r="B24" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="I20" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="K20" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="L20" s="6" t="s">
+      <c r="H24" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="K24" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="M20" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="25" t="s">
+      <c r="L24" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="N24" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="P24" s="28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="A25" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="O20" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
-      <c r="A21" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="G21" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="25" t="s">
+      <c r="D25" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="17">
         <v>10</v>
       </c>
-      <c r="I21" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="L21" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M21" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="N21" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="O21" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="P21" s="25" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
-      <c r="A22" s="25" t="s">
+      <c r="F25" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="I25" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="6">
-        <v>60</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I22" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="L22" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="O22" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="P22" s="25" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16">
-      <c r="A23" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="G23" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="H23" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="I23" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="J23" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="K23" s="6">
-        <v>13</v>
-      </c>
-      <c r="L23" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="M23" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="N23" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="O23" s="6">
-        <v>14</v>
-      </c>
-      <c r="P23" s="25" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
-      <c r="A24" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="H24" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L24" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="M24" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="N24" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="O24" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="P24" s="25" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16">
-      <c r="A25" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" s="6">
-        <v>10</v>
-      </c>
-      <c r="F25" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="H25" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="I25" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="J25" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="K25" s="6">
+      <c r="J25" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="K25" s="17">
         <v>11</v>
       </c>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/byteCodeDemo.xlsx
+++ b/byteCodeDemo.xlsx
@@ -494,34 +494,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="A20" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>johnny.fei:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="57">
   <si>
     <t>CA</t>
   </si>
@@ -661,22 +639,37 @@
     <t>0E</t>
   </si>
   <si>
+    <t>0B</t>
+  </si>
+  <si>
     <t>字段计数器</t>
   </si>
   <si>
-    <t>0B</t>
-  </si>
-  <si>
     <t>0D</t>
   </si>
   <si>
+    <t>字段访问标识</t>
+  </si>
+  <si>
     <t>3D</t>
   </si>
   <si>
     <t>B4</t>
   </si>
   <si>
+    <t>字段名索引</t>
+  </si>
+  <si>
     <t>AC</t>
+  </si>
+  <si>
+    <t>字段描述符索引</t>
+  </si>
+  <si>
+    <t>字段的属性计数器</t>
+  </si>
+  <si>
+    <t>方法计数器</t>
   </si>
 </sst>
 </file>
@@ -860,7 +853,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="48">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -917,7 +910,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.35"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1240,7 +1269,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1264,16 +1293,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1282,89 +1311,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1416,13 +1445,43 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
@@ -1449,7 +1508,28 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2006,19 +2086,19 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="21" t="s">
+      <c r="E1" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="31" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="3">
         <v>34</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="32" t="s">
         <v>4</v>
       </c>
       <c r="J1" s="4">
@@ -2027,60 +2107,60 @@
       <c r="K1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="23" t="s">
+      <c r="L1" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="23" t="s">
+      <c r="N1" s="33" t="s">
         <v>4</v>
       </c>
       <c r="O1" s="5">
         <v>12</v>
       </c>
-      <c r="P1" s="24" t="s">
+      <c r="P1" s="34" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="24" t="s">
+      <c r="A2" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="34" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="6">
         <v>13</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="33" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="5">
         <v>14</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="H2" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="I2" s="34" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="6">
         <v>15</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="M2" s="23" t="s">
+      <c r="L2" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="33" t="s">
         <v>8</v>
       </c>
       <c r="N2" s="5" t="s">
@@ -2097,25 +2177,25 @@
       </c>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="24" t="s">
+      <c r="B3" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="34" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="6">
         <v>49</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="23" t="s">
+      <c r="F3" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="33" t="s">
         <v>14</v>
       </c>
       <c r="H3" s="5" t="s">
@@ -2136,13 +2216,13 @@
       <c r="M3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="24" t="s">
+      <c r="N3" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="P3" s="24" t="s">
+      <c r="O3" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="34" t="s">
         <v>8</v>
       </c>
       <c r="S3" s="8" t="s">
@@ -2162,13 +2242,13 @@
       <c r="C4" s="6">
         <v>56</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="23" t="s">
+      <c r="E4" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="33" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="5">
@@ -2183,10 +2263,10 @@
       <c r="J4" s="5">
         <v>65</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="K4" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="24" t="s">
+      <c r="L4" s="34" t="s">
         <v>4</v>
       </c>
       <c r="M4" s="6" t="s">
@@ -2242,10 +2322,10 @@
       <c r="L5" s="6">
         <v>65</v>
       </c>
-      <c r="M5" s="23" t="s">
+      <c r="M5" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="23" t="s">
+      <c r="N5" s="33" t="s">
         <v>4</v>
       </c>
       <c r="O5" s="5">
@@ -2318,13 +2398,13 @@
       <c r="A7" s="5">
         <v>65</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="24" t="s">
+      <c r="C7" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="34" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="6">
@@ -2339,10 +2419,10 @@
       <c r="H7" s="6">
         <v>73</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="I7" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="23" t="s">
+      <c r="J7" s="33" t="s">
         <v>4</v>
       </c>
       <c r="K7" s="5">
@@ -2421,13 +2501,13 @@
       <c r="B9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="24" t="s">
+      <c r="D9" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="34" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="6">
@@ -2439,13 +2519,13 @@
       <c r="H9" s="6">
         <v>64</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="I9" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="23" t="s">
+      <c r="J9" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="33" t="s">
         <v>8</v>
       </c>
       <c r="L9" s="5">
@@ -2457,10 +2537,10 @@
       <c r="N9" s="5">
         <v>49</v>
       </c>
-      <c r="O9" s="24" t="s">
+      <c r="O9" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="P9" s="24" t="s">
+      <c r="P9" s="34" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2498,13 +2578,13 @@
       <c r="K10" s="6">
         <v>65</v>
       </c>
-      <c r="L10" s="23" t="s">
+      <c r="L10" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="M10" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="N10" s="23" t="s">
+      <c r="M10" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="33" t="s">
         <v>7</v>
       </c>
       <c r="O10" s="5">
@@ -2539,39 +2619,39 @@
       <c r="H11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="J11" s="24" t="s">
+      <c r="I11" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="24" t="s">
+      <c r="K11" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" s="34" t="s">
         <v>33</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O11" s="23" t="s">
+      <c r="N11" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="O11" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="P11" s="23" t="s">
+      <c r="P11" s="33" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:20">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="34" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="6">
@@ -2642,10 +2722,10 @@
       <c r="I13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="23" t="s">
+      <c r="J13" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="23" t="s">
+      <c r="K13" s="33" t="s">
         <v>4</v>
       </c>
       <c r="L13" s="5">
@@ -2701,16 +2781,16 @@
       <c r="L14" s="13">
         <v>74</v>
       </c>
-      <c r="M14" s="25" t="s">
+      <c r="M14" s="35" t="s">
         <v>4</v>
       </c>
       <c r="N14" s="14">
         <v>21</v>
       </c>
-      <c r="O14" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" s="21" t="s">
+      <c r="O14" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="31" t="s">
         <v>8</v>
       </c>
       <c r="S14" s="15" t="s">
@@ -2718,106 +2798,106 @@
       </c>
     </row>
     <row r="15" spans="1:20">
-      <c r="A15" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="24" t="s">
+      <c r="A15" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="27" t="s">
+      <c r="C15" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="28" t="s">
+      <c r="G15" s="38" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="I15" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="28" t="s">
+      <c r="I15" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="K15" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="28" t="s">
+      <c r="K15" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="L15" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="M15" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="28" t="s">
+      <c r="M15" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="42" t="s">
         <v>37</v>
       </c>
       <c r="S15" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="T15" s="18"/>
+      <c r="T15" s="22"/>
     </row>
     <row r="16" spans="1:20">
-      <c r="A16" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="28" t="s">
+      <c r="A16" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="G16" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="I16" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="J16" s="28" t="s">
+      <c r="I16" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="J16" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="K16" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="L16" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="M16" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="N16" s="17">
+      <c r="K16" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="L16" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="M16" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="N16" s="23">
         <v>38</v>
       </c>
-      <c r="O16" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="P16" s="28" t="s">
+      <c r="O16" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="P16" s="43" t="s">
         <v>37</v>
       </c>
       <c r="S16" s="11" t="s">
@@ -2825,52 +2905,52 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="28" t="s">
+      <c r="A17" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="17" t="s">
+      <c r="C17" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="17" t="s">
+      <c r="G17" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="17" t="s">
+      <c r="H17" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="I17" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="28" t="s">
+      <c r="I17" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="K17" s="17" t="s">
+      <c r="K17" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="L17" s="28" t="s">
+      <c r="L17" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="M17" s="17" t="s">
+      <c r="M17" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="N17" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="O17" s="28" t="s">
+      <c r="N17" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="P17" s="17" t="s">
+      <c r="P17" s="23" t="s">
         <v>43</v>
       </c>
       <c r="S17" s="7" t="s">
@@ -2878,397 +2958,413 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="28" t="s">
+      <c r="A18" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="17" t="s">
+      <c r="E18" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="17" t="s">
+      <c r="G18" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="K18" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="28" t="s">
+      <c r="K18" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="M18" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="17" t="s">
+      <c r="M18" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="S18" s="19" t="s">
-        <v>46</v>
-      </c>
+      <c r="S18" s="22"/>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="28" t="s">
+      <c r="A19" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="17">
+      <c r="C19" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="23">
         <v>10</v>
       </c>
-      <c r="E19" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F19" s="17" t="s">
+      <c r="E19" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="J19" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="L19" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="M19" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="N19" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="O19" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="P19" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="S19" s="16" t="s">
         <v>47</v>
-      </c>
-      <c r="G19" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H19" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="I19" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="K19" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="L19" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="M19" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="N19" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="O19" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="P19" s="17" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="17" t="s">
+      <c r="A20" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="17" t="s">
+      <c r="C20" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="28" t="s">
+      <c r="E20" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="I20" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="17" t="s">
+      <c r="I20" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="K20" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="L20" s="17" t="s">
+      <c r="K20" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="M20" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="28" t="s">
+      <c r="M20" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="O20" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="28" t="s">
+      <c r="O20" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="43" t="s">
         <v>7</v>
+      </c>
+      <c r="S20" s="26" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="28" t="s">
+      <c r="A21" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="G21" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="28" t="s">
+      <c r="G21" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="I21" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="L21" s="17" t="s">
+      <c r="I21" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="M21" s="17" t="s">
+      <c r="M21" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="N21" s="17" t="s">
+      <c r="N21" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="O21" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="P21" s="28" t="s">
-        <v>4</v>
+      <c r="O21" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="P21" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="18" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:19">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="23">
         <v>60</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="E22" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="28" t="s">
+      <c r="E22" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="G22" s="17" t="s">
+      <c r="G22" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="H22" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="I22" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="28" t="s">
+      <c r="H22" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="I22" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="K22" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="L22" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="O22" s="28" t="s">
+      <c r="K22" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="L22" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="P22" s="28" t="s">
-        <v>4</v>
+      <c r="P22" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="27" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:19">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="17" t="s">
+      <c r="B23" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="F23" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="G23" s="28" t="s">
+      <c r="F23" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="H23" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="I23" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="J23" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="K23" s="17">
+      <c r="H23" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="23">
         <v>13</v>
       </c>
-      <c r="L23" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="M23" s="17" t="s">
+      <c r="L23" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="N23" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="O23" s="17">
+      <c r="N23" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="23">
         <v>14</v>
       </c>
-      <c r="P23" s="28" t="s">
-        <v>4</v>
+      <c r="P23" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="28" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="17" t="s">
+      <c r="A24" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="28" t="s">
+      <c r="F24" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="H24" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="17" t="s">
+      <c r="H24" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="K24" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="L24" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="M24" s="17" t="s">
+      <c r="L24" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="N24" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="O24" s="17" t="s">
+      <c r="N24" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="P24" s="28" t="s">
+      <c r="P24" s="43" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="28" t="s">
+      <c r="A25" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" s="17">
+      <c r="D25" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="23">
         <v>10</v>
       </c>
-      <c r="F25" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H25" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="I25" s="28" t="s">
+      <c r="F25" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="I25" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="J25" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="K25" s="17">
+      <c r="J25" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="K25" s="23">
         <v>11</v>
       </c>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="23"/>
+      <c r="O25" s="23"/>
+      <c r="P25" s="23"/>
+      <c r="S25" s="29" t="s">
+        <v>56</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/byteCodeDemo.xlsx
+++ b/byteCodeDemo.xlsx
@@ -499,7 +499,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="61">
   <si>
     <t>CA</t>
   </si>
@@ -670,6 +670,18 @@
   </si>
   <si>
     <t>方法计数器</t>
+  </si>
+  <si>
+    <t>方法的访问标识</t>
+  </si>
+  <si>
+    <t>方法名索引</t>
+  </si>
+  <si>
+    <t>方法描述符索引</t>
+  </si>
+  <si>
+    <t>方法的属性计数器</t>
   </si>
 </sst>
 </file>
@@ -853,7 +865,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="48">
+  <fills count="51">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -941,6 +953,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB41CAF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1269,7 +1299,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1293,16 +1323,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1311,89 +1341,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1463,13 +1493,22 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
@@ -1484,6 +1523,18 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1523,13 +1574,22 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1799,6 +1859,11 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <mruColors>
+      <color rgb="00B41CAF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2065,7 +2130,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T25"/>
+  <dimension ref="A1:T29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="19" max="19" width="24.125" customWidth="1"/>
@@ -2086,19 +2151,19 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="31" t="s">
+      <c r="E1" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="38" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="3">
         <v>34</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="39" t="s">
         <v>4</v>
       </c>
       <c r="J1" s="4">
@@ -2107,60 +2172,60 @@
       <c r="K1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="33" t="s">
+      <c r="L1" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="33" t="s">
+      <c r="N1" s="40" t="s">
         <v>4</v>
       </c>
       <c r="O1" s="5">
         <v>12</v>
       </c>
-      <c r="P1" s="34" t="s">
+      <c r="P1" s="41" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="34" t="s">
+      <c r="A2" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="41" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="6">
         <v>13</v>
       </c>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="40" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="5">
         <v>14</v>
       </c>
-      <c r="H2" s="34" t="s">
+      <c r="H2" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="I2" s="41" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="6">
         <v>15</v>
       </c>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="M2" s="33" t="s">
+      <c r="L2" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="40" t="s">
         <v>8</v>
       </c>
       <c r="N2" s="5" t="s">
@@ -2177,25 +2242,25 @@
       </c>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="34" t="s">
+      <c r="B3" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="41" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="6">
         <v>49</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="33" t="s">
+      <c r="F3" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="40" t="s">
         <v>14</v>
       </c>
       <c r="H3" s="5" t="s">
@@ -2216,13 +2281,13 @@
       <c r="M3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="34" t="s">
+      <c r="N3" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="P3" s="34" t="s">
+      <c r="O3" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="41" t="s">
         <v>8</v>
       </c>
       <c r="S3" s="8" t="s">
@@ -2242,13 +2307,13 @@
       <c r="C4" s="6">
         <v>56</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="33" t="s">
+      <c r="E4" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="40" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="5">
@@ -2263,10 +2328,10 @@
       <c r="J4" s="5">
         <v>65</v>
       </c>
-      <c r="K4" s="34" t="s">
+      <c r="K4" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="34" t="s">
+      <c r="L4" s="41" t="s">
         <v>4</v>
       </c>
       <c r="M4" s="6" t="s">
@@ -2322,10 +2387,10 @@
       <c r="L5" s="6">
         <v>65</v>
       </c>
-      <c r="M5" s="33" t="s">
+      <c r="M5" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="33" t="s">
+      <c r="N5" s="40" t="s">
         <v>4</v>
       </c>
       <c r="O5" s="5">
@@ -2398,13 +2463,13 @@
       <c r="A7" s="5">
         <v>65</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="34" t="s">
+      <c r="C7" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="41" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="6">
@@ -2419,10 +2484,10 @@
       <c r="H7" s="6">
         <v>73</v>
       </c>
-      <c r="I7" s="33" t="s">
+      <c r="I7" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="33" t="s">
+      <c r="J7" s="40" t="s">
         <v>4</v>
       </c>
       <c r="K7" s="5">
@@ -2501,13 +2566,13 @@
       <c r="B9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="34" t="s">
+      <c r="D9" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="41" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="6">
@@ -2519,13 +2584,13 @@
       <c r="H9" s="6">
         <v>64</v>
       </c>
-      <c r="I9" s="33" t="s">
+      <c r="I9" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="33" t="s">
+      <c r="J9" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="40" t="s">
         <v>8</v>
       </c>
       <c r="L9" s="5">
@@ -2537,10 +2602,10 @@
       <c r="N9" s="5">
         <v>49</v>
       </c>
-      <c r="O9" s="34" t="s">
+      <c r="O9" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="P9" s="34" t="s">
+      <c r="P9" s="41" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2578,13 +2643,13 @@
       <c r="K10" s="6">
         <v>65</v>
       </c>
-      <c r="L10" s="33" t="s">
+      <c r="L10" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="M10" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="N10" s="33" t="s">
+      <c r="M10" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="40" t="s">
         <v>7</v>
       </c>
       <c r="O10" s="5">
@@ -2619,39 +2684,39 @@
       <c r="H11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="J11" s="34" t="s">
+      <c r="I11" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="34" t="s">
+      <c r="K11" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" s="41" t="s">
         <v>33</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="O11" s="33" t="s">
+      <c r="N11" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="O11" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="P11" s="33" t="s">
+      <c r="P11" s="40" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:20">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="41" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="6">
@@ -2722,10 +2787,10 @@
       <c r="I13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="33" t="s">
+      <c r="J13" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="33" t="s">
+      <c r="K13" s="40" t="s">
         <v>4</v>
       </c>
       <c r="L13" s="5">
@@ -2781,16 +2846,16 @@
       <c r="L14" s="13">
         <v>74</v>
       </c>
-      <c r="M14" s="35" t="s">
+      <c r="M14" s="42" t="s">
         <v>4</v>
       </c>
       <c r="N14" s="14">
         <v>21</v>
       </c>
-      <c r="O14" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" s="31" t="s">
+      <c r="O14" s="38" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="38" t="s">
         <v>8</v>
       </c>
       <c r="S14" s="15" t="s">
@@ -2798,52 +2863,52 @@
       </c>
     </row>
     <row r="15" spans="1:20">
-      <c r="A15" s="34" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="34" t="s">
+      <c r="A15" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="37" t="s">
+      <c r="C15" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="38" t="s">
+      <c r="G15" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="I15" s="39" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="39" t="s">
+      <c r="I15" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="K15" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="40" t="s">
+      <c r="K15" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="L15" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="M15" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="42" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="42" t="s">
+      <c r="M15" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="49" t="s">
         <v>37</v>
       </c>
       <c r="S15" s="9" t="s">
@@ -2852,52 +2917,52 @@
       <c r="T15" s="22"/>
     </row>
     <row r="16" spans="1:20">
-      <c r="A16" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="43" t="s">
+      <c r="A16" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="43" t="s">
+      <c r="C16" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="43" t="s">
+      <c r="E16" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="G16" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="43" t="s">
+      <c r="G16" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="I16" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="J16" s="43" t="s">
+      <c r="I16" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="J16" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="K16" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="L16" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="M16" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="N16" s="23">
+      <c r="K16" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="L16" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="M16" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="N16" s="26">
         <v>38</v>
       </c>
-      <c r="O16" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="P16" s="43" t="s">
+      <c r="O16" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="P16" s="53" t="s">
         <v>37</v>
       </c>
       <c r="S16" s="11" t="s">
@@ -2905,52 +2970,52 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="43" t="s">
+      <c r="A17" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="23" t="s">
+      <c r="C17" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="23" t="s">
+      <c r="G17" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="H17" s="23" t="s">
+      <c r="H17" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="I17" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="43" t="s">
+      <c r="I17" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="K17" s="23" t="s">
+      <c r="K17" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="L17" s="43" t="s">
+      <c r="L17" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="M17" s="23" t="s">
+      <c r="M17" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="N17" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="O17" s="43" t="s">
+      <c r="N17" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="P17" s="23" t="s">
+      <c r="P17" s="26" t="s">
         <v>43</v>
       </c>
       <c r="S17" s="7" t="s">
@@ -2958,103 +3023,103 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="43" t="s">
+      <c r="A18" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="23" t="s">
+      <c r="E18" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="23" t="s">
+      <c r="G18" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="K18" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="43" t="s">
+      <c r="K18" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="M18" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="23" t="s">
+      <c r="M18" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="26" t="s">
         <v>45</v>
       </c>
       <c r="S18" s="22"/>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="43" t="s">
+      <c r="A19" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="23">
+      <c r="C19" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="26">
         <v>10</v>
       </c>
-      <c r="E19" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="F19" s="23" t="s">
+      <c r="E19" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="G19" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="H19" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="I19" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="J19" s="23" t="s">
+      <c r="G19" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="J19" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="K19" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="L19" s="43" t="s">
+      <c r="K19" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="L19" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="M19" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="N19" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="O19" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="P19" s="23" t="s">
+      <c r="M19" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="N19" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="O19" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="P19" s="26" t="s">
         <v>5</v>
       </c>
       <c r="S19" s="16" t="s">
@@ -3062,105 +3127,105 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="23" t="s">
+      <c r="A20" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="23" t="s">
+      <c r="C20" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="44" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="43" t="s">
+      <c r="E20" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="I20" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="23" t="s">
+      <c r="I20" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="K20" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="L20" s="23" t="s">
+      <c r="K20" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M20" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="43" t="s">
+      <c r="M20" s="52" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="O20" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="43" t="s">
+      <c r="O20" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="S20" s="26" t="s">
+      <c r="S20" s="29" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="23" t="s">
+      <c r="A21" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="E21" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="43" t="s">
+      <c r="E21" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="G21" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="43" t="s">
+      <c r="G21" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="I21" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="L21" s="23" t="s">
+      <c r="I21" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="M21" s="23" t="s">
+      <c r="M21" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="N21" s="23" t="s">
+      <c r="N21" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="O21" s="23" t="s">
+      <c r="O21" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="P21" s="43" t="s">
+      <c r="P21" s="53" t="s">
         <v>4</v>
       </c>
       <c r="S21" s="18" t="s">
@@ -3168,202 +3233,222 @@
       </c>
     </row>
     <row r="22" spans="1:19">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="43" t="s">
+      <c r="B22" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="23">
+      <c r="C22" s="26">
         <v>60</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="E22" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="43" t="s">
+      <c r="E22" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="G22" s="23" t="s">
+      <c r="G22" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="H22" s="23" t="s">
+      <c r="H22" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="43" t="s">
+      <c r="I22" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="K22" s="23" t="s">
+      <c r="K22" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="L22" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="O22" s="43" t="s">
+      <c r="L22" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="P22" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="S22" s="27" t="s">
+      <c r="P22" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="30" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:19">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="23" t="s">
+      <c r="B23" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="F23" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="G23" s="43" t="s">
+      <c r="F23" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="H23" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="I23" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="J23" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="K23" s="23">
+      <c r="H23" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="26">
         <v>13</v>
       </c>
-      <c r="L23" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="M23" s="23" t="s">
+      <c r="L23" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="N23" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="O23" s="23">
+      <c r="N23" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="26">
         <v>14</v>
       </c>
-      <c r="P23" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="S23" s="28" t="s">
+      <c r="P23" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="31" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="23" t="s">
+      <c r="B24" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="43" t="s">
+      <c r="F24" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="H24" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="23" t="s">
+      <c r="H24" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="K24" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="L24" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="M24" s="23" t="s">
+      <c r="L24" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="N24" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="O24" s="23" t="s">
+      <c r="N24" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="P24" s="43" t="s">
+      <c r="P24" s="53" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="44" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="43" t="s">
+      <c r="A25" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" s="23">
+      <c r="D25" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="26">
         <v>10</v>
       </c>
-      <c r="F25" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="H25" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="I25" s="43" t="s">
+      <c r="F25" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="I25" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="J25" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="K25" s="23">
+      <c r="J25" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="K25" s="26">
         <v>11</v>
       </c>
-      <c r="L25" s="23"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="23"/>
-      <c r="O25" s="23"/>
-      <c r="P25" s="23"/>
-      <c r="S25" s="29" t="s">
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="26"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="26"/>
+      <c r="S25" s="32" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="S26" s="33" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="S27" s="34" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
+      <c r="S28" s="35" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
+      <c r="S29" s="36" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/byteCodeDemo.xlsx
+++ b/byteCodeDemo.xlsx
@@ -499,7 +499,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="69">
   <si>
     <t>CA</t>
   </si>
@@ -621,6 +621,9 @@
     <t>父类索引</t>
   </si>
   <si>
+    <t>属性名索引</t>
+  </si>
+  <si>
     <t>2A</t>
   </si>
   <si>
@@ -636,21 +639,33 @@
     <t>实现的接口计数器</t>
   </si>
   <si>
+    <t>属性长度</t>
+  </si>
+  <si>
     <t>0E</t>
   </si>
   <si>
+    <t>操作数栈的最大深度</t>
+  </si>
+  <si>
     <t>0B</t>
   </si>
   <si>
     <t>字段计数器</t>
   </si>
   <si>
+    <t>局部变量表的长度</t>
+  </si>
+  <si>
     <t>0D</t>
   </si>
   <si>
     <t>字段访问标识</t>
   </si>
   <si>
+    <t>字节码指令的长度</t>
+  </si>
+  <si>
     <t>3D</t>
   </si>
   <si>
@@ -660,13 +675,22 @@
     <t>字段名索引</t>
   </si>
   <si>
+    <t>具体的字节码指令</t>
+  </si>
+  <si>
     <t>AC</t>
   </si>
   <si>
     <t>字段描述符索引</t>
   </si>
   <si>
+    <t>异常表的长度</t>
+  </si>
+  <si>
     <t>字段的属性计数器</t>
+  </si>
+  <si>
+    <t>code中的属性计数器</t>
   </si>
   <si>
     <t>方法计数器</t>
@@ -694,7 +718,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -705,6 +729,62 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7" tint="0.4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="0.4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="0.4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFB41CAF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFF43308"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7E0145"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7CDB05"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0766D4"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -854,12 +934,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1293,137 +1373,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1502,9 +1582,48 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1514,12 +1633,24 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1581,6 +1712,30 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
@@ -1862,6 +2017,11 @@
   <colors>
     <mruColors>
       <color rgb="00B41CAF"/>
+      <color rgb="00F43308"/>
+      <color rgb="0068045E"/>
+      <color rgb="007E0145"/>
+      <color rgb="007CDB05"/>
+      <color rgb="000766D4"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2133,9 +2293,9 @@
   <dimension ref="A1:T29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="19" max="19" width="24.125" customWidth="1"/>
-    <col min="20" max="20" width="25.375" customWidth="1"/>
-    <col min="21" max="21" width="31.25" customWidth="1"/>
+    <col min="18" max="18" width="21.375" customWidth="1"/>
+    <col min="19" max="19" width="13.375" customWidth="1"/>
+    <col min="20" max="20" width="31.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -2151,19 +2311,19 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="38" t="s">
+      <c r="E1" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="55" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="3">
         <v>34</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="I1" s="56" t="s">
         <v>4</v>
       </c>
       <c r="J1" s="4">
@@ -2172,60 +2332,60 @@
       <c r="K1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="40" t="s">
+      <c r="L1" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="40" t="s">
+      <c r="N1" s="57" t="s">
         <v>4</v>
       </c>
       <c r="O1" s="5">
         <v>12</v>
       </c>
-      <c r="P1" s="41" t="s">
+      <c r="P1" s="58" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="41" t="s">
+      <c r="A2" s="58" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="58" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="6">
         <v>13</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="57" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="5">
         <v>14</v>
       </c>
-      <c r="H2" s="41" t="s">
+      <c r="H2" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="41" t="s">
+      <c r="I2" s="58" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="6">
         <v>15</v>
       </c>
-      <c r="K2" s="40" t="s">
+      <c r="K2" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="M2" s="40" t="s">
+      <c r="L2" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="57" t="s">
         <v>8</v>
       </c>
       <c r="N2" s="5" t="s">
@@ -2237,30 +2397,30 @@
       <c r="P2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="7" t="s">
+      <c r="R2" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="41" t="s">
+      <c r="B3" s="58" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="58" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="6">
         <v>49</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="40" t="s">
+      <c r="F3" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="57" t="s">
         <v>14</v>
       </c>
       <c r="H3" s="5" t="s">
@@ -2281,19 +2441,19 @@
       <c r="M3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="41" t="s">
+      <c r="N3" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="P3" s="41" t="s">
+      <c r="O3" s="58" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="S3" s="8" t="s">
+      <c r="R3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="T3" t="s">
+      <c r="S3" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2307,13 +2467,13 @@
       <c r="C4" s="6">
         <v>56</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="40" t="s">
+      <c r="E4" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="57" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="5">
@@ -2328,10 +2488,10 @@
       <c r="J4" s="5">
         <v>65</v>
       </c>
-      <c r="K4" s="41" t="s">
+      <c r="K4" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="41" t="s">
+      <c r="L4" s="58" t="s">
         <v>4</v>
       </c>
       <c r="M4" s="6" t="s">
@@ -2346,7 +2506,7 @@
       <c r="P4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="S4" s="9" t="s">
+      <c r="R4" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2387,10 +2547,10 @@
       <c r="L5" s="6">
         <v>65</v>
       </c>
-      <c r="M5" s="40" t="s">
+      <c r="M5" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="40" t="s">
+      <c r="N5" s="57" t="s">
         <v>4</v>
       </c>
       <c r="O5" s="5">
@@ -2399,7 +2559,7 @@
       <c r="P5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="S5" s="10" t="s">
+      <c r="R5" s="10" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2452,10 +2612,10 @@
       <c r="P6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="S6" s="11" t="s">
+      <c r="R6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="T6" s="12" t="s">
+      <c r="S6" s="12" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2463,13 +2623,13 @@
       <c r="A7" s="5">
         <v>65</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="41" t="s">
+      <c r="C7" s="58" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="58" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="6">
@@ -2484,10 +2644,10 @@
       <c r="H7" s="6">
         <v>73</v>
       </c>
-      <c r="I7" s="40" t="s">
+      <c r="I7" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="40" t="s">
+      <c r="J7" s="57" t="s">
         <v>4</v>
       </c>
       <c r="K7" s="5">
@@ -2566,13 +2726,13 @@
       <c r="B9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="41" t="s">
+      <c r="D9" s="58" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="58" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="6">
@@ -2584,13 +2744,13 @@
       <c r="H9" s="6">
         <v>64</v>
       </c>
-      <c r="I9" s="40" t="s">
+      <c r="I9" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="40" t="s">
+      <c r="J9" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="57" t="s">
         <v>8</v>
       </c>
       <c r="L9" s="5">
@@ -2602,10 +2762,10 @@
       <c r="N9" s="5">
         <v>49</v>
       </c>
-      <c r="O9" s="41" t="s">
+      <c r="O9" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="P9" s="41" t="s">
+      <c r="P9" s="58" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2643,13 +2803,13 @@
       <c r="K10" s="6">
         <v>65</v>
       </c>
-      <c r="L10" s="40" t="s">
+      <c r="L10" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="M10" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="N10" s="40" t="s">
+      <c r="M10" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="57" t="s">
         <v>7</v>
       </c>
       <c r="O10" s="5">
@@ -2684,39 +2844,39 @@
       <c r="H11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="J11" s="41" t="s">
+      <c r="I11" s="58" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="41" t="s">
+      <c r="K11" s="58" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" s="58" t="s">
         <v>33</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="O11" s="40" t="s">
+      <c r="N11" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="O11" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="P11" s="40" t="s">
+      <c r="P11" s="57" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:20">
-      <c r="A12" s="40" t="s">
+      <c r="A12" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="58" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="6">
@@ -2787,10 +2947,10 @@
       <c r="I13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="40" t="s">
+      <c r="J13" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="40" t="s">
+      <c r="K13" s="57" t="s">
         <v>4</v>
       </c>
       <c r="L13" s="5">
@@ -2846,614 +3006,638 @@
       <c r="L14" s="13">
         <v>74</v>
       </c>
-      <c r="M14" s="42" t="s">
+      <c r="M14" s="59" t="s">
         <v>4</v>
       </c>
       <c r="N14" s="14">
         <v>21</v>
       </c>
-      <c r="O14" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" s="38" t="s">
+      <c r="O14" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="15" t="s">
+      <c r="R14" s="15" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:20">
-      <c r="A15" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="41" t="s">
+      <c r="A15" s="58" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="44" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="44" t="s">
+      <c r="C15" s="60" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="60" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="61" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="45" t="s">
+      <c r="G15" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="I15" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="46" t="s">
+      <c r="I15" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="K15" s="47" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="47" t="s">
+      <c r="K15" s="64" t="s">
+        <v>4</v>
+      </c>
+      <c r="L15" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="M15" s="48" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="48" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="49" t="s">
+      <c r="M15" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="S15" s="9" t="s">
+      <c r="R15" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="T15" s="22"/>
+      <c r="S15" s="22"/>
     </row>
     <row r="16" spans="1:20">
-      <c r="A16" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="50" t="s">
+      <c r="A16" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="44" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="44" t="s">
+      <c r="C16" s="61" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="48" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="51" t="s">
+      <c r="E16" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="G16" s="52" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="52" t="s">
+      <c r="G16" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="I16" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="J16" s="53" t="s">
+      <c r="I16" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="J16" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="K16" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="L16" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="M16" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="N16" s="26">
+      <c r="K16" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="L16" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="M16" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="N16" s="28">
         <v>38</v>
       </c>
-      <c r="O16" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="P16" s="53" t="s">
+      <c r="O16" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="P16" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="S16" s="11" t="s">
+      <c r="R16" s="11" t="s">
         <v>39</v>
       </c>
+      <c r="T16" s="30" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="17" spans="1:19">
-      <c r="A17" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="53" t="s">
+    <row r="17" spans="1:20">
+      <c r="A17" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="26" t="s">
+      <c r="C17" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="H17" s="26" t="s">
+      <c r="G17" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="I17" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="53" t="s">
+      <c r="H17" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="I17" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="K17" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="L17" s="53" t="s">
+      <c r="K17" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="L17" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="M17" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="N17" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="O17" s="53" t="s">
+      <c r="M17" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="N17" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="P17" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="S17" s="7" t="s">
+      <c r="P17" s="33" t="s">
         <v>44</v>
       </c>
+      <c r="R17" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="T17" s="34" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="18" spans="1:19">
-      <c r="A18" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="53" t="s">
+    <row r="18" spans="1:20">
+      <c r="A18" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="77" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="77" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="26" t="s">
+      <c r="E18" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="J18" s="26" t="s">
+      <c r="G18" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="J18" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="K18" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="53" t="s">
+      <c r="K18" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="M18" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="S18" s="22"/>
+      <c r="M18" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="R18" s="22"/>
+      <c r="T18" s="38" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="19" spans="1:19">
-      <c r="A19" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="53" t="s">
+    <row r="19" spans="1:20">
+      <c r="A19" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="26">
+      <c r="C19" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="37">
         <v>10</v>
       </c>
-      <c r="E19" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="G19" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="H19" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="I19" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="J19" s="26" t="s">
+      <c r="E19" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="J19" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="K19" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="L19" s="53" t="s">
+      <c r="K19" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="L19" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="M19" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="N19" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="O19" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="P19" s="26" t="s">
+      <c r="M19" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="N19" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="O19" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="P19" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="S19" s="16" t="s">
+      <c r="R19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="T19" s="39" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="A20" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="80" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" s="61" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="16" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="20" spans="1:19">
-      <c r="A20" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="55" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="I20" s="44" t="s">
-        <v>4</v>
-      </c>
-      <c r="J20" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="K20" s="51" t="s">
+      <c r="K20" s="68" t="s">
         <v>4</v>
       </c>
       <c r="L20" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M20" s="52" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="52" t="s">
+      <c r="M20" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="O20" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="53" t="s">
+      <c r="O20" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="S20" s="29" t="s">
+      <c r="R20" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="T20" s="43" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
+      <c r="A21" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="M21" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="N21" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="O21" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="P21" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="T21" s="44" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
+      <c r="A22" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="78" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="37">
+        <v>60</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="I22" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="K22" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="L22" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="P22" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="T22" s="46" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
+      <c r="A23" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="37">
+        <v>13</v>
+      </c>
+      <c r="L23" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="37">
+        <v>14</v>
+      </c>
+      <c r="P23" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="T23" s="48" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20">
+      <c r="A24" s="37" t="s">
         <v>49</v>
       </c>
+      <c r="B24" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="K24" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="N24" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="P24" s="78" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="21" spans="1:19">
-      <c r="A21" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="G21" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="53" t="s">
+    <row r="25" spans="1:20">
+      <c r="A25" s="80" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="I21" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="L21" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="M21" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="N21" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="O21" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="P21" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="S21" s="18" t="s">
-        <v>52</v>
+      <c r="D25" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="37">
+        <v>10</v>
+      </c>
+      <c r="F25" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="I25" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="J25" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="K25" s="37">
+        <v>11</v>
+      </c>
+      <c r="L25" s="37"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="R25" s="49" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
-      <c r="A22" s="53" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="26">
-        <v>60</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="E22" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="53" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="H22" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="I22" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="53" t="s">
-        <v>37</v>
-      </c>
-      <c r="K22" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="L22" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="O22" s="53" t="s">
-        <v>37</v>
-      </c>
-      <c r="P22" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="S22" s="30" t="s">
-        <v>54</v>
+    <row r="26" spans="1:20">
+      <c r="R26" s="50" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
-      <c r="A23" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="G23" s="53" t="s">
-        <v>37</v>
-      </c>
-      <c r="H23" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="I23" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="J23" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="K23" s="26">
-        <v>13</v>
-      </c>
-      <c r="L23" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="M23" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="N23" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="O23" s="26">
-        <v>14</v>
-      </c>
-      <c r="P23" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="S23" s="31" t="s">
-        <v>55</v>
+    <row r="27" spans="1:20">
+      <c r="R27" s="51" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
-      <c r="A24" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="H24" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="L24" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="M24" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="N24" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="O24" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="P24" s="53" t="s">
-        <v>4</v>
+    <row r="28" spans="1:20">
+      <c r="R28" s="52" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
-      <c r="A25" s="55" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" s="26">
-        <v>10</v>
-      </c>
-      <c r="F25" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="H25" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="I25" s="53" t="s">
-        <v>37</v>
-      </c>
-      <c r="J25" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="K25" s="26">
-        <v>11</v>
-      </c>
-      <c r="L25" s="26"/>
-      <c r="M25" s="26"/>
-      <c r="N25" s="26"/>
-      <c r="O25" s="26"/>
-      <c r="P25" s="26"/>
-      <c r="S25" s="32" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19">
-      <c r="S26" s="33" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19">
-      <c r="S27" s="34" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19">
-      <c r="S28" s="35" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19">
-      <c r="S29" s="36" t="s">
-        <v>60</v>
+    <row r="29" spans="1:20">
+      <c r="R29" s="53" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="S3:S4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/byteCodeDemo.xlsx
+++ b/byteCodeDemo.xlsx
@@ -499,7 +499,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="81">
   <si>
     <t>CA</t>
   </si>
@@ -693,19 +693,55 @@
     <t>code中的属性计数器</t>
   </si>
   <si>
+    <t>code中的属性名索引</t>
+  </si>
+  <si>
     <t>方法计数器</t>
   </si>
   <si>
+    <t>属性的长度</t>
+  </si>
+  <si>
     <t>方法的访问标识</t>
   </si>
   <si>
+    <t>line_number_table的长度</t>
+  </si>
+  <si>
     <t>方法名索引</t>
   </si>
   <si>
+    <t>start pc</t>
+  </si>
+  <si>
     <t>方法描述符索引</t>
   </si>
   <si>
+    <t>line number</t>
+  </si>
+  <si>
     <t>方法的属性计数器</t>
+  </si>
+  <si>
+    <t>local_variable_table的length</t>
+  </si>
+  <si>
+    <t>附加属性计数器</t>
+  </si>
+  <si>
+    <t>local_variable_table的变量名的索引</t>
+  </si>
+  <si>
+    <t>属性名的索引</t>
+  </si>
+  <si>
+    <t>local_variable_table的变量的描述符索引</t>
+  </si>
+  <si>
+    <t>local_variable_table的变量的index</t>
+  </si>
+  <si>
+    <t>源码文件索引</t>
   </si>
 </sst>
 </file>
@@ -718,7 +754,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -785,6 +821,62 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0766D4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0FB746"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFF6FC14"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF463794"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7" tint="-0.25"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4C2799"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF970943"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1D41D5"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -934,18 +1026,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="51">
+  <fills count="54">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1057,6 +1149,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1373,137 +1483,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1588,9 +1698,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1615,21 +1722,45 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1651,21 +1782,57 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1738,13 +1905,46 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2016,12 +2216,16 @@
   </tableStyles>
   <colors>
     <mruColors>
-      <color rgb="00B41CAF"/>
-      <color rgb="00F43308"/>
       <color rgb="0068045E"/>
       <color rgb="007E0145"/>
       <color rgb="007CDB05"/>
       <color rgb="000766D4"/>
+      <color rgb="000FB746"/>
+      <color rgb="00F6FC14"/>
+      <color rgb="00463794"/>
+      <color rgb="004C2799"/>
+      <color rgb="00970943"/>
+      <color rgb="001D41D5"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2290,12 +2494,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T29"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="18" max="18" width="21.375" customWidth="1"/>
     <col min="19" max="19" width="13.375" customWidth="1"/>
-    <col min="20" max="20" width="31.25" customWidth="1"/>
+    <col min="20" max="20" width="38.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -2311,19 +2515,19 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="55" t="s">
+      <c r="E1" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="74" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="3">
         <v>34</v>
       </c>
-      <c r="I1" s="56" t="s">
+      <c r="I1" s="75" t="s">
         <v>4</v>
       </c>
       <c r="J1" s="4">
@@ -2332,60 +2536,60 @@
       <c r="K1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="57" t="s">
+      <c r="L1" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="57" t="s">
+      <c r="N1" s="76" t="s">
         <v>4</v>
       </c>
       <c r="O1" s="5">
         <v>12</v>
       </c>
-      <c r="P1" s="58" t="s">
+      <c r="P1" s="77" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" s="58" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="58" t="s">
+      <c r="A2" s="77" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="77" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="6">
         <v>13</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="76" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="5">
         <v>14</v>
       </c>
-      <c r="H2" s="58" t="s">
+      <c r="H2" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="77" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="6">
         <v>15</v>
       </c>
-      <c r="K2" s="57" t="s">
+      <c r="K2" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="M2" s="57" t="s">
+      <c r="L2" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="76" t="s">
         <v>8</v>
       </c>
       <c r="N2" s="5" t="s">
@@ -2402,25 +2606,25 @@
       </c>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="58" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="58" t="s">
+      <c r="B3" s="77" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="77" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="6">
         <v>49</v>
       </c>
-      <c r="E3" s="57" t="s">
+      <c r="E3" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="57" t="s">
+      <c r="F3" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="76" t="s">
         <v>14</v>
       </c>
       <c r="H3" s="5" t="s">
@@ -2441,13 +2645,13 @@
       <c r="M3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="58" t="s">
+      <c r="N3" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="58" t="s">
-        <v>4</v>
-      </c>
-      <c r="P3" s="58" t="s">
+      <c r="O3" s="77" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="77" t="s">
         <v>8</v>
       </c>
       <c r="R3" s="8" t="s">
@@ -2467,13 +2671,13 @@
       <c r="C4" s="6">
         <v>56</v>
       </c>
-      <c r="D4" s="57" t="s">
+      <c r="D4" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="57" t="s">
+      <c r="E4" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="76" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="5">
@@ -2488,10 +2692,10 @@
       <c r="J4" s="5">
         <v>65</v>
       </c>
-      <c r="K4" s="58" t="s">
+      <c r="K4" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="58" t="s">
+      <c r="L4" s="77" t="s">
         <v>4</v>
       </c>
       <c r="M4" s="6" t="s">
@@ -2547,10 +2751,10 @@
       <c r="L5" s="6">
         <v>65</v>
       </c>
-      <c r="M5" s="57" t="s">
+      <c r="M5" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="57" t="s">
+      <c r="N5" s="76" t="s">
         <v>4</v>
       </c>
       <c r="O5" s="5">
@@ -2623,13 +2827,13 @@
       <c r="A7" s="5">
         <v>65</v>
       </c>
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="58" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="58" t="s">
+      <c r="C7" s="77" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="77" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="6">
@@ -2644,10 +2848,10 @@
       <c r="H7" s="6">
         <v>73</v>
       </c>
-      <c r="I7" s="57" t="s">
+      <c r="I7" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="57" t="s">
+      <c r="J7" s="76" t="s">
         <v>4</v>
       </c>
       <c r="K7" s="5">
@@ -2726,13 +2930,13 @@
       <c r="B9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="58" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="58" t="s">
+      <c r="D9" s="77" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="77" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="6">
@@ -2744,13 +2948,13 @@
       <c r="H9" s="6">
         <v>64</v>
       </c>
-      <c r="I9" s="57" t="s">
+      <c r="I9" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="57" t="s">
+      <c r="J9" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="76" t="s">
         <v>8</v>
       </c>
       <c r="L9" s="5">
@@ -2762,10 +2966,10 @@
       <c r="N9" s="5">
         <v>49</v>
       </c>
-      <c r="O9" s="58" t="s">
+      <c r="O9" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="P9" s="58" t="s">
+      <c r="P9" s="77" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2803,13 +3007,13 @@
       <c r="K10" s="6">
         <v>65</v>
       </c>
-      <c r="L10" s="57" t="s">
+      <c r="L10" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="M10" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="N10" s="57" t="s">
+      <c r="M10" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="76" t="s">
         <v>7</v>
       </c>
       <c r="O10" s="5">
@@ -2844,39 +3048,39 @@
       <c r="H11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="58" t="s">
-        <v>4</v>
-      </c>
-      <c r="J11" s="58" t="s">
+      <c r="I11" s="77" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="58" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="58" t="s">
+      <c r="K11" s="77" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" s="77" t="s">
         <v>33</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="O11" s="57" t="s">
+      <c r="N11" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="O11" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="P11" s="57" t="s">
+      <c r="P11" s="76" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:20">
-      <c r="A12" s="57" t="s">
+      <c r="A12" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="77" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="6">
@@ -2947,10 +3151,10 @@
       <c r="I13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="57" t="s">
+      <c r="J13" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="57" t="s">
+      <c r="K13" s="76" t="s">
         <v>4</v>
       </c>
       <c r="L13" s="5">
@@ -3006,16 +3210,16 @@
       <c r="L14" s="13">
         <v>74</v>
       </c>
-      <c r="M14" s="59" t="s">
+      <c r="M14" s="78" t="s">
         <v>4</v>
       </c>
       <c r="N14" s="14">
         <v>21</v>
       </c>
-      <c r="O14" s="55" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" s="55" t="s">
+      <c r="O14" s="74" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="74" t="s">
         <v>8</v>
       </c>
       <c r="R14" s="15" t="s">
@@ -3023,52 +3227,52 @@
       </c>
     </row>
     <row r="15" spans="1:20">
-      <c r="A15" s="58" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="58" t="s">
+      <c r="A15" s="77" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="60" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="60" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="61" t="s">
+      <c r="C15" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="80" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="62" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="62" t="s">
+      <c r="G15" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="I15" s="63" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="63" t="s">
+      <c r="I15" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="K15" s="64" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="64" t="s">
+      <c r="K15" s="83" t="s">
+        <v>4</v>
+      </c>
+      <c r="L15" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="M15" s="65" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="65" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="66" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="66" t="s">
+      <c r="M15" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="85" t="s">
         <v>37</v>
       </c>
       <c r="R15" s="9" t="s">
@@ -3077,562 +3281,612 @@
       <c r="S15" s="22"/>
     </row>
     <row r="16" spans="1:20">
-      <c r="A16" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="67" t="s">
+      <c r="A16" s="86" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="61" t="s">
+      <c r="C16" s="80" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="65" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="68" t="s">
+      <c r="E16" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="G16" s="69" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="69" t="s">
+      <c r="G16" s="88" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="I16" s="70" t="s">
-        <v>4</v>
-      </c>
-      <c r="J16" s="70" t="s">
+      <c r="I16" s="89" t="s">
+        <v>4</v>
+      </c>
+      <c r="J16" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="K16" s="71" t="s">
-        <v>4</v>
-      </c>
-      <c r="L16" s="71" t="s">
-        <v>4</v>
-      </c>
-      <c r="M16" s="71" t="s">
-        <v>4</v>
-      </c>
-      <c r="N16" s="28">
+      <c r="K16" s="90" t="s">
+        <v>4</v>
+      </c>
+      <c r="L16" s="90" t="s">
+        <v>4</v>
+      </c>
+      <c r="M16" s="90" t="s">
+        <v>4</v>
+      </c>
+      <c r="N16" s="27">
         <v>38</v>
       </c>
-      <c r="O16" s="72" t="s">
-        <v>4</v>
-      </c>
-      <c r="P16" s="72" t="s">
+      <c r="O16" s="91" t="s">
+        <v>4</v>
+      </c>
+      <c r="P16" s="91" t="s">
         <v>37</v>
       </c>
       <c r="R16" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="T16" s="30" t="s">
+      <c r="T16" s="29" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:20">
-      <c r="A17" s="73" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="73" t="s">
+    <row r="17" spans="1:21">
+      <c r="A17" s="92" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="74" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="74" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="74" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="32" t="s">
+      <c r="C17" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G17" s="33" t="s">
+      <c r="G17" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="H17" s="33" t="s">
+      <c r="H17" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="I17" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="75" t="s">
+      <c r="I17" s="94" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="K17" s="33" t="s">
+      <c r="K17" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="L17" s="75" t="s">
+      <c r="L17" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="M17" s="33" t="s">
+      <c r="M17" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="N17" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="O17" s="75" t="s">
+      <c r="N17" s="94" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="P17" s="33" t="s">
+      <c r="P17" s="32" t="s">
         <v>44</v>
       </c>
       <c r="R17" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="T17" s="34" t="s">
+      <c r="T17" s="33" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:20">
-      <c r="A18" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="77" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="77" t="s">
+    <row r="18" spans="1:21">
+      <c r="A18" s="95" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="95" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="96" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="37" t="s">
+      <c r="E18" s="97" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="78" t="s">
+      <c r="G18" s="98" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="98" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="98" t="s">
         <v>4</v>
       </c>
       <c r="J18" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="K18" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="78" t="s">
+      <c r="K18" s="99" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="M18" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" s="37" t="s">
+      <c r="M18" s="100" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="100" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="101" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="40" t="s">
         <v>47</v>
       </c>
       <c r="R18" s="22"/>
-      <c r="T18" s="38" t="s">
+      <c r="T18" s="41" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:20">
-      <c r="A19" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="78" t="s">
+    <row r="19" spans="1:21">
+      <c r="A19" s="100" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="37">
+      <c r="C19" s="101" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="40">
         <v>10</v>
       </c>
-      <c r="E19" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="F19" s="37" t="s">
+      <c r="E19" s="97" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="G19" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="H19" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="I19" s="78" t="s">
+      <c r="G19" s="98" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="98" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="98" t="s">
         <v>4</v>
       </c>
       <c r="J19" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="K19" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="L19" s="78" t="s">
+      <c r="K19" s="99" t="s">
+        <v>4</v>
+      </c>
+      <c r="L19" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="M19" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="N19" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="O19" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="P19" s="37" t="s">
+      <c r="M19" s="100" t="s">
+        <v>4</v>
+      </c>
+      <c r="N19" s="100" t="s">
+        <v>4</v>
+      </c>
+      <c r="O19" s="102" t="s">
+        <v>4</v>
+      </c>
+      <c r="P19" s="42" t="s">
         <v>5</v>
       </c>
       <c r="R19" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="T19" s="39" t="s">
+      <c r="T19" s="43" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:20">
-      <c r="A20" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="37" t="s">
+    <row r="20" spans="1:21">
+      <c r="A20" s="103" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="37" t="s">
+      <c r="C20" s="104" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="E20" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="80" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="67" t="s">
+      <c r="E20" s="105" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="86" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="I20" s="61" t="s">
+      <c r="I20" s="80" t="s">
         <v>4</v>
       </c>
       <c r="J20" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="K20" s="68" t="s">
+      <c r="K20" s="87" t="s">
         <v>4</v>
       </c>
       <c r="L20" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M20" s="69" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="69" t="s">
+      <c r="M20" s="88" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="O20" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="78" t="s">
+      <c r="O20" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="R20" s="42" t="s">
+      <c r="R20" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="T20" s="43" t="s">
+      <c r="T20" s="50" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:20">
-      <c r="A21" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="37" t="s">
+    <row r="21" spans="1:21">
+      <c r="A21" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="E21" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="78" t="s">
+      <c r="E21" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="G21" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="78" t="s">
+      <c r="G21" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="I21" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="L21" s="37" t="s">
+      <c r="I21" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="L21" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="M21" s="37" t="s">
+      <c r="M21" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="N21" s="37" t="s">
+      <c r="N21" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="O21" s="37" t="s">
+      <c r="O21" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="P21" s="78" t="s">
+      <c r="P21" s="107" t="s">
         <v>4</v>
       </c>
       <c r="R21" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="T21" s="44" t="s">
+      <c r="T21" s="51" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:20">
-      <c r="A22" s="78" t="s">
+    <row r="22" spans="1:21">
+      <c r="A22" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="78" t="s">
+      <c r="B22" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="37">
+      <c r="C22" s="48">
         <v>60</v>
       </c>
-      <c r="D22" s="37" t="s">
+      <c r="D22" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="78" t="s">
+      <c r="E22" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="G22" s="37" t="s">
+      <c r="G22" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="H22" s="37" t="s">
+      <c r="H22" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="I22" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="78" t="s">
+      <c r="I22" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="K22" s="37" t="s">
+      <c r="K22" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="L22" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="O22" s="78" t="s">
+      <c r="L22" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="P22" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="R22" s="45" t="s">
+      <c r="P22" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="T22" s="46" t="s">
+      <c r="T22" s="53" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:20">
-      <c r="A23" s="37" t="s">
+    <row r="23" spans="1:21">
+      <c r="A23" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="37" t="s">
+      <c r="B23" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F23" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="G23" s="78" t="s">
+      <c r="F23" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="H23" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="I23" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="J23" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="K23" s="37">
+      <c r="H23" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="K23" s="48">
         <v>13</v>
       </c>
-      <c r="L23" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="M23" s="37" t="s">
+      <c r="L23" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="M23" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="N23" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="O23" s="37">
+      <c r="N23" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="O23" s="48">
         <v>14</v>
       </c>
-      <c r="P23" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="R23" s="47" t="s">
+      <c r="P23" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="T23" s="48" t="s">
+      <c r="T23" s="55" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:20">
-      <c r="A24" s="37" t="s">
+    <row r="24" spans="1:21">
+      <c r="A24" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="37" t="s">
+      <c r="B24" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="78" t="s">
+      <c r="F24" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="H24" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="37" t="s">
+      <c r="H24" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="K24" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="L24" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="M24" s="37" t="s">
+      <c r="L24" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="N24" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="O24" s="37" t="s">
+      <c r="N24" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="O24" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="P24" s="78" t="s">
-        <v>4</v>
-      </c>
+      <c r="P24" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="T24" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="U24" s="36"/>
     </row>
-    <row r="25" spans="1:20">
-      <c r="A25" s="80" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="78" t="s">
+    <row r="25" spans="1:21">
+      <c r="A25" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="108" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" s="37">
+      <c r="D25" s="110" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="58">
         <v>10</v>
       </c>
-      <c r="F25" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="H25" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="I25" s="78" t="s">
+      <c r="F25" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="I25" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="J25" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="K25" s="37">
+      <c r="J25" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="K25" s="20">
         <v>11</v>
       </c>
-      <c r="L25" s="37"/>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="P25" s="37"/>
-      <c r="R25" s="49" t="s">
-        <v>64</v>
+      <c r="L25" s="48"/>
+      <c r="M25" s="48"/>
+      <c r="N25" s="48"/>
+      <c r="O25" s="48"/>
+      <c r="P25" s="48"/>
+      <c r="R25" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="T25" s="60" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:20">
-      <c r="R26" s="50" t="s">
-        <v>65</v>
+    <row r="26" spans="1:21">
+      <c r="R26" s="61" t="s">
+        <v>67</v>
+      </c>
+      <c r="T26" s="62" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:20">
-      <c r="R27" s="51" t="s">
+    <row r="27" spans="1:21">
+      <c r="R27" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="T27" s="64" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
+      <c r="R28" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="T28" s="66" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
+      <c r="R29" s="67" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
+      <c r="T30" s="68" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
+      <c r="R31" s="69" t="s">
+        <v>75</v>
+      </c>
+      <c r="T31" s="70" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
+      <c r="R32" s="71" t="s">
+        <v>77</v>
+      </c>
+      <c r="T32" s="72" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33" spans="18:20">
+      <c r="R33" s="12" t="s">
         <v>66</v>
       </c>
+      <c r="T33" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="28" spans="1:20">
-      <c r="R28" s="52" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20">
-      <c r="R29" s="53" t="s">
-        <v>68</v>
+    <row r="34" spans="18:20">
+      <c r="R34" s="54" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/byteCodeDemo.xlsx
+++ b/byteCodeDemo.xlsx
@@ -540,7 +540,7 @@
     <t>6D</t>
   </si>
   <si>
-    <t xml:space="preserve"> 魔数</t>
+    <t>魔数</t>
   </si>
   <si>
     <t>06</t>
@@ -1037,7 +1037,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="54">
+  <fills count="53">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1149,12 +1149,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1489,7 +1483,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1513,16 +1507,16 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1531,89 +1525,89 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1788,9 +1782,6 @@
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1827,7 +1818,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1942,9 +1933,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2515,19 +2503,19 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="73" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="73" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="74" t="s">
+      <c r="E1" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="73" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="3">
         <v>34</v>
       </c>
-      <c r="I1" s="75" t="s">
+      <c r="I1" s="74" t="s">
         <v>4</v>
       </c>
       <c r="J1" s="4">
@@ -2536,60 +2524,60 @@
       <c r="K1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="76" t="s">
+      <c r="L1" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="76" t="s">
+      <c r="N1" s="75" t="s">
         <v>4</v>
       </c>
       <c r="O1" s="5">
         <v>12</v>
       </c>
-      <c r="P1" s="77" t="s">
+      <c r="P1" s="76" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" s="77" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="77" t="s">
+      <c r="A2" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="77" t="s">
+      <c r="C2" s="76" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="6">
         <v>13</v>
       </c>
-      <c r="E2" s="76" t="s">
+      <c r="E2" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="76" t="s">
+      <c r="F2" s="75" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="5">
         <v>14</v>
       </c>
-      <c r="H2" s="77" t="s">
+      <c r="H2" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="77" t="s">
+      <c r="I2" s="76" t="s">
         <v>4</v>
       </c>
       <c r="J2" s="6">
         <v>15</v>
       </c>
-      <c r="K2" s="76" t="s">
+      <c r="K2" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="M2" s="76" t="s">
+      <c r="L2" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="75" t="s">
         <v>8</v>
       </c>
       <c r="N2" s="5" t="s">
@@ -2606,25 +2594,25 @@
       </c>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="77" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="77" t="s">
+      <c r="B3" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="76" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="6">
         <v>49</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="E3" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="76" t="s">
+      <c r="F3" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="75" t="s">
         <v>14</v>
       </c>
       <c r="H3" s="5" t="s">
@@ -2645,13 +2633,13 @@
       <c r="M3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="77" t="s">
+      <c r="N3" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="77" t="s">
-        <v>4</v>
-      </c>
-      <c r="P3" s="77" t="s">
+      <c r="O3" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="76" t="s">
         <v>8</v>
       </c>
       <c r="R3" s="8" t="s">
@@ -2671,13 +2659,13 @@
       <c r="C4" s="6">
         <v>56</v>
       </c>
-      <c r="D4" s="76" t="s">
+      <c r="D4" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="76" t="s">
+      <c r="E4" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="75" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="5">
@@ -2692,10 +2680,10 @@
       <c r="J4" s="5">
         <v>65</v>
       </c>
-      <c r="K4" s="77" t="s">
+      <c r="K4" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="77" t="s">
+      <c r="L4" s="76" t="s">
         <v>4</v>
       </c>
       <c r="M4" s="6" t="s">
@@ -2751,10 +2739,10 @@
       <c r="L5" s="6">
         <v>65</v>
       </c>
-      <c r="M5" s="76" t="s">
+      <c r="M5" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="76" t="s">
+      <c r="N5" s="75" t="s">
         <v>4</v>
       </c>
       <c r="O5" s="5">
@@ -2827,13 +2815,13 @@
       <c r="A7" s="5">
         <v>65</v>
       </c>
-      <c r="B7" s="77" t="s">
+      <c r="B7" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="77" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="77" t="s">
+      <c r="C7" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="76" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="6">
@@ -2848,10 +2836,10 @@
       <c r="H7" s="6">
         <v>73</v>
       </c>
-      <c r="I7" s="76" t="s">
+      <c r="I7" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="J7" s="76" t="s">
+      <c r="J7" s="75" t="s">
         <v>4</v>
       </c>
       <c r="K7" s="5">
@@ -2930,13 +2918,13 @@
       <c r="B9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="77" t="s">
+      <c r="C9" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="77" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="77" t="s">
+      <c r="D9" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="76" t="s">
         <v>8</v>
       </c>
       <c r="F9" s="6">
@@ -2948,13 +2936,13 @@
       <c r="H9" s="6">
         <v>64</v>
       </c>
-      <c r="I9" s="76" t="s">
+      <c r="I9" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="K9" s="76" t="s">
+      <c r="J9" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="75" t="s">
         <v>8</v>
       </c>
       <c r="L9" s="5">
@@ -2966,10 +2954,10 @@
       <c r="N9" s="5">
         <v>49</v>
       </c>
-      <c r="O9" s="77" t="s">
+      <c r="O9" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="P9" s="77" t="s">
+      <c r="P9" s="76" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3007,13 +2995,13 @@
       <c r="K10" s="6">
         <v>65</v>
       </c>
-      <c r="L10" s="76" t="s">
+      <c r="L10" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="M10" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="N10" s="76" t="s">
+      <c r="M10" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="N10" s="75" t="s">
         <v>7</v>
       </c>
       <c r="O10" s="5">
@@ -3048,39 +3036,39 @@
       <c r="H11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="77" t="s">
-        <v>4</v>
-      </c>
-      <c r="J11" s="77" t="s">
+      <c r="I11" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="J11" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="K11" s="77" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="77" t="s">
+      <c r="K11" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="L11" s="76" t="s">
         <v>33</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="N11" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="O11" s="76" t="s">
+      <c r="N11" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="O11" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="P11" s="76" t="s">
+      <c r="P11" s="75" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:20">
-      <c r="A12" s="76" t="s">
+      <c r="A12" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="77" t="s">
+      <c r="B12" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="77" t="s">
+      <c r="C12" s="76" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="6">
@@ -3151,10 +3139,10 @@
       <c r="I13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="76" t="s">
+      <c r="J13" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="76" t="s">
+      <c r="K13" s="75" t="s">
         <v>4</v>
       </c>
       <c r="L13" s="5">
@@ -3210,16 +3198,16 @@
       <c r="L14" s="13">
         <v>74</v>
       </c>
-      <c r="M14" s="78" t="s">
+      <c r="M14" s="77" t="s">
         <v>4</v>
       </c>
       <c r="N14" s="14">
         <v>21</v>
       </c>
-      <c r="O14" s="74" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" s="74" t="s">
+      <c r="O14" s="73" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="73" t="s">
         <v>8</v>
       </c>
       <c r="R14" s="15" t="s">
@@ -3227,52 +3215,52 @@
       </c>
     </row>
     <row r="15" spans="1:20">
-      <c r="A15" s="77" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="77" t="s">
+      <c r="A15" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="80" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="80" t="s">
+      <c r="C15" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="78" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="81" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="81" t="s">
+      <c r="G15" s="80" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="I15" s="82" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="82" t="s">
+      <c r="I15" s="81" t="s">
+        <v>4</v>
+      </c>
+      <c r="J15" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="K15" s="83" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="83" t="s">
+      <c r="K15" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="L15" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="M15" s="84" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="84" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="85" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="85" t="s">
+      <c r="M15" s="83" t="s">
+        <v>4</v>
+      </c>
+      <c r="N15" s="83" t="s">
+        <v>4</v>
+      </c>
+      <c r="O15" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="84" t="s">
         <v>37</v>
       </c>
       <c r="R15" s="9" t="s">
@@ -3281,52 +3269,52 @@
       <c r="S15" s="22"/>
     </row>
     <row r="16" spans="1:20">
-      <c r="A16" s="86" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="86" t="s">
+      <c r="A16" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="80" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="80" t="s">
+      <c r="C16" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="84" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="87" t="s">
+      <c r="E16" s="83" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="86" t="s">
         <v>33</v>
       </c>
-      <c r="G16" s="88" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="88" t="s">
+      <c r="G16" s="87" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="I16" s="89" t="s">
-        <v>4</v>
-      </c>
-      <c r="J16" s="89" t="s">
+      <c r="I16" s="88" t="s">
+        <v>4</v>
+      </c>
+      <c r="J16" s="88" t="s">
         <v>7</v>
       </c>
-      <c r="K16" s="90" t="s">
-        <v>4</v>
-      </c>
-      <c r="L16" s="90" t="s">
-        <v>4</v>
-      </c>
-      <c r="M16" s="90" t="s">
+      <c r="K16" s="89" t="s">
+        <v>4</v>
+      </c>
+      <c r="L16" s="89" t="s">
+        <v>4</v>
+      </c>
+      <c r="M16" s="89" t="s">
         <v>4</v>
       </c>
       <c r="N16" s="27">
         <v>38</v>
       </c>
-      <c r="O16" s="91" t="s">
-        <v>4</v>
-      </c>
-      <c r="P16" s="91" t="s">
+      <c r="O16" s="90" t="s">
+        <v>4</v>
+      </c>
+      <c r="P16" s="90" t="s">
         <v>37</v>
       </c>
       <c r="R16" s="11" t="s">
@@ -3337,19 +3325,19 @@
       </c>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="92" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="92" t="s">
+      <c r="A17" s="91" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="91" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="93" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="93" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="93" t="s">
+      <c r="C17" s="92" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="92" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="92" t="s">
         <v>4</v>
       </c>
       <c r="F17" s="31" t="s">
@@ -3361,25 +3349,25 @@
       <c r="H17" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="I17" s="94" t="s">
-        <v>4</v>
-      </c>
-      <c r="J17" s="94" t="s">
+      <c r="I17" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="J17" s="93" t="s">
         <v>10</v>
       </c>
       <c r="K17" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="L17" s="94" t="s">
+      <c r="L17" s="93" t="s">
         <v>6</v>
       </c>
       <c r="M17" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="N17" s="94" t="s">
-        <v>4</v>
-      </c>
-      <c r="O17" s="94" t="s">
+      <c r="N17" s="93" t="s">
+        <v>4</v>
+      </c>
+      <c r="O17" s="93" t="s">
         <v>37</v>
       </c>
       <c r="P17" s="32" t="s">
@@ -3393,49 +3381,49 @@
       </c>
     </row>
     <row r="18" spans="1:21">
-      <c r="A18" s="95" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="95" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="96" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="96" t="s">
+      <c r="A18" s="94" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="94" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="95" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="97" t="s">
+      <c r="E18" s="96" t="s">
         <v>4</v>
       </c>
       <c r="F18" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="G18" s="98" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="98" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="98" t="s">
+      <c r="G18" s="97" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="97" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="97" t="s">
         <v>4</v>
       </c>
       <c r="J18" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="K18" s="99" t="s">
-        <v>4</v>
-      </c>
-      <c r="L18" s="99" t="s">
+      <c r="K18" s="98" t="s">
+        <v>4</v>
+      </c>
+      <c r="L18" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="M18" s="100" t="s">
-        <v>4</v>
-      </c>
-      <c r="N18" s="100" t="s">
-        <v>4</v>
-      </c>
-      <c r="O18" s="101" t="s">
+      <c r="M18" s="99" t="s">
+        <v>4</v>
+      </c>
+      <c r="N18" s="99" t="s">
+        <v>4</v>
+      </c>
+      <c r="O18" s="100" t="s">
         <v>4</v>
       </c>
       <c r="P18" s="40" t="s">
@@ -3447,49 +3435,49 @@
       </c>
     </row>
     <row r="19" spans="1:21">
-      <c r="A19" s="100" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="100" t="s">
+      <c r="A19" s="99" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="101" t="s">
+      <c r="C19" s="100" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="40">
         <v>10</v>
       </c>
-      <c r="E19" s="97" t="s">
+      <c r="E19" s="96" t="s">
         <v>4</v>
       </c>
       <c r="F19" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="G19" s="98" t="s">
-        <v>4</v>
-      </c>
-      <c r="H19" s="98" t="s">
-        <v>4</v>
-      </c>
-      <c r="I19" s="98" t="s">
+      <c r="G19" s="97" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="97" t="s">
+        <v>4</v>
+      </c>
+      <c r="I19" s="97" t="s">
         <v>4</v>
       </c>
       <c r="J19" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="K19" s="99" t="s">
-        <v>4</v>
-      </c>
-      <c r="L19" s="99" t="s">
+      <c r="K19" s="98" t="s">
+        <v>4</v>
+      </c>
+      <c r="L19" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="M19" s="100" t="s">
-        <v>4</v>
-      </c>
-      <c r="N19" s="100" t="s">
-        <v>4</v>
-      </c>
-      <c r="O19" s="102" t="s">
+      <c r="M19" s="99" t="s">
+        <v>4</v>
+      </c>
+      <c r="N19" s="99" t="s">
+        <v>4</v>
+      </c>
+      <c r="O19" s="101" t="s">
         <v>4</v>
       </c>
       <c r="P19" s="42" t="s">
@@ -3503,52 +3491,52 @@
       </c>
     </row>
     <row r="20" spans="1:21">
-      <c r="A20" s="103" t="s">
+      <c r="A20" s="102" t="s">
         <v>4</v>
       </c>
       <c r="B20" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="104" t="s">
+      <c r="C20" s="103" t="s">
         <v>4</v>
       </c>
       <c r="D20" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="E20" s="105" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="106" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="86" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="86" t="s">
+      <c r="E20" s="104" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="105" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="I20" s="80" t="s">
+      <c r="I20" s="79" t="s">
         <v>4</v>
       </c>
       <c r="J20" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="K20" s="87" t="s">
+      <c r="K20" s="86" t="s">
         <v>4</v>
       </c>
       <c r="L20" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="M20" s="88" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="88" t="s">
+      <c r="M20" s="87" t="s">
+        <v>4</v>
+      </c>
+      <c r="N20" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="O20" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="P20" s="107" t="s">
+      <c r="O20" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="106" t="s">
         <v>7</v>
       </c>
       <c r="R20" s="49" t="s">
@@ -3559,37 +3547,37 @@
       </c>
     </row>
     <row r="21" spans="1:21">
-      <c r="A21" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="107" t="s">
+      <c r="A21" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="106" t="s">
         <v>4</v>
       </c>
       <c r="D21" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="E21" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="107" t="s">
+      <c r="E21" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="G21" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="107" t="s">
+      <c r="G21" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="I21" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="K21" s="107" t="s">
+      <c r="I21" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="K21" s="106" t="s">
         <v>4</v>
       </c>
       <c r="L21" s="48" t="s">
@@ -3604,7 +3592,7 @@
       <c r="O21" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="P21" s="107" t="s">
+      <c r="P21" s="106" t="s">
         <v>4</v>
       </c>
       <c r="R21" s="18" t="s">
@@ -3615,10 +3603,10 @@
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="A22" s="107" t="s">
+      <c r="A22" s="106" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="107" t="s">
+      <c r="B22" s="106" t="s">
         <v>34</v>
       </c>
       <c r="C22" s="48">
@@ -3627,10 +3615,10 @@
       <c r="D22" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="107" t="s">
+      <c r="E22" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="106" t="s">
         <v>37</v>
       </c>
       <c r="G22" s="48" t="s">
@@ -3639,28 +3627,28 @@
       <c r="H22" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="I22" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="J22" s="107" t="s">
+      <c r="I22" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="106" t="s">
         <v>37</v>
       </c>
       <c r="K22" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="L22" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="M22" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="N22" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="O22" s="107" t="s">
+      <c r="L22" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="M22" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="N22" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="O22" s="106" t="s">
         <v>37</v>
       </c>
-      <c r="P22" s="107" t="s">
+      <c r="P22" s="106" t="s">
         <v>4</v>
       </c>
       <c r="R22" s="52" t="s">
@@ -3674,49 +3662,49 @@
       <c r="A23" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="107" t="s">
+      <c r="B23" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="106" t="s">
         <v>4</v>
       </c>
       <c r="E23" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="F23" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="G23" s="107" t="s">
+      <c r="F23" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" s="106" t="s">
         <v>37</v>
       </c>
-      <c r="H23" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="I23" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="J23" s="107" t="s">
+      <c r="H23" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="I23" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="J23" s="106" t="s">
         <v>4</v>
       </c>
       <c r="K23" s="48">
         <v>13</v>
       </c>
-      <c r="L23" s="107" t="s">
+      <c r="L23" s="106" t="s">
         <v>4</v>
       </c>
       <c r="M23" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="N23" s="107" t="s">
+      <c r="N23" s="106" t="s">
         <v>4</v>
       </c>
       <c r="O23" s="48">
         <v>14</v>
       </c>
-      <c r="P23" s="107" t="s">
+      <c r="P23" s="106" t="s">
         <v>4</v>
       </c>
       <c r="R23" s="54" t="s">
@@ -3730,49 +3718,49 @@
       <c r="A24" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="107" t="s">
+      <c r="B24" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="106" t="s">
         <v>4</v>
       </c>
       <c r="E24" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24" s="107" t="s">
+      <c r="F24" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="H24" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="I24" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="107" t="s">
+      <c r="H24" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="106" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="106" t="s">
         <v>4</v>
       </c>
       <c r="K24" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="L24" s="107" t="s">
+      <c r="L24" s="106" t="s">
         <v>4</v>
       </c>
       <c r="M24" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="N24" s="107" t="s">
+      <c r="N24" s="106" t="s">
         <v>4</v>
       </c>
       <c r="O24" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="P24" s="107" t="s">
+      <c r="P24" s="106" t="s">
         <v>4</v>
       </c>
       <c r="T24" s="36" t="s">
@@ -3781,34 +3769,34 @@
       <c r="U24" s="36"/>
     </row>
     <row r="25" spans="1:21">
-      <c r="A25" s="106" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="108" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="109" t="s">
+      <c r="A25" s="105" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="110" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" s="58">
+      <c r="D25" s="108" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="57">
         <v>10</v>
       </c>
-      <c r="F25" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="H25" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="I25" s="76" t="s">
+      <c r="F25" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="I25" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="J25" s="84" t="s">
+      <c r="J25" s="83" t="s">
         <v>4</v>
       </c>
       <c r="K25" s="20">
@@ -3819,60 +3807,60 @@
       <c r="N25" s="48"/>
       <c r="O25" s="48"/>
       <c r="P25" s="48"/>
-      <c r="R25" s="59" t="s">
+      <c r="R25" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="T25" s="60" t="s">
+      <c r="T25" s="59" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:21">
-      <c r="R26" s="61" t="s">
+      <c r="R26" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="T26" s="62" t="s">
+      <c r="T26" s="61" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:21">
-      <c r="R27" s="63" t="s">
+      <c r="R27" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="T27" s="64" t="s">
+      <c r="T27" s="63" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:21">
-      <c r="R28" s="65" t="s">
+      <c r="R28" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="T28" s="66" t="s">
+      <c r="T28" s="65" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:21">
-      <c r="R29" s="67" t="s">
+      <c r="R29" s="66" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:21">
-      <c r="T30" s="68" t="s">
+      <c r="T30" s="67" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:21">
-      <c r="R31" s="69" t="s">
+      <c r="R31" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="T31" s="70" t="s">
+      <c r="T31" s="69" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:21">
-      <c r="R32" s="71" t="s">
+      <c r="R32" s="70" t="s">
         <v>77</v>
       </c>
-      <c r="T32" s="72" t="s">
+      <c r="T32" s="71" t="s">
         <v>78</v>
       </c>
     </row>
